--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit b373025 (built 2026-10-15 15:22 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 9000ab0 (built 2026-10-15 16:06 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b373025 · built 2026-10-15 15:22 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 9000ab0 (built 2026-10-15 16:06 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 232c17d (built 2026-10-15 16:51 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 9000ab0 · built 2026-10-15 16:06 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 232c17d (built 2026-10-15 16:51 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 47e0b89 (built 2026-10-16 13:14 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 232c17d · built 2026-10-15 16:51 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 47e0b89 (built 2026-10-16 13:14 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 1eb4564 (built 2026-10-19 09:56 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 47e0b89 · built 2026-10-16 13:14 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 1eb4564 (built 2026-10-19 09:56 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit ae2eabb (built 2026-10-19 10:13 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 1eb4564 · built 2026-10-19 09:56 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit ae2eabb (built 2026-10-19 10:13 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit a02e58b (built 2026-10-19 11:55 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit ae2eabb · built 2026-10-19 10:13 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit a02e58b (built 2026-10-19 11:55 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 70c4cff (built 2026-10-19 12:11 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit a02e58b · built 2026-10-19 11:55 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 70c4cff (built 2026-10-19 12:11 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 8353c43 (built 2026-10-19 13:11 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 70c4cff · built 2026-10-19 12:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 8353c43 (built 2026-10-19 13:11 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit b02b579 (built 2026-10-19 17:33 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 8353c43 · built 2026-10-19 13:11 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit b02b579 (built 2026-10-19 17:33 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 54cc0be (built 2026-10-19 17:40 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7369,7 +7369,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12350,7 +12350,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14483,7 +14483,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27252,7 +27252,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28562,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29154,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32465,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33647,7 +33647,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35142,7 +35142,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37310,7 +37310,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42583,7 +42583,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -46793,7 +46793,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit b02b579 · built 2026-10-19 17:33 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/draft/testing-criteria-scorecard-unreleased-draft.xlsx
+++ b/draft/testing-criteria-scorecard-unreleased-draft.xlsx
@@ -1800,7 +1800,7 @@
     <row r="3" ht="42" customHeight="1" s="125">
       <c r="B3" s="128" t="inlineStr">
         <is>
-          <t>DRAFT — Version unreleased draft · branch main · commit 54cc0be (built 2026-10-19 17:40 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
+          <t>DRAFT — Version unreleased draft · branch main · commit 35e735e (built 2026-10-26 11:18 PHT). Thresholds and policy values are PROPOSED — for DOH approval. Definitions, the Technical Baseline (TB-), Terminology &amp; Registry Sources (SRC-), FHIR Traceability (TR-), Indicator Definitions (IND-), Certification &amp; Revalidation rules and the Glossary are in the companion document "HIE System Validation — Technical Reference Guide" (the Reference Guide).</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2300,7 +2300,7 @@
     <row r="2" ht="79.5" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>Baseline technical safeguards required before live patient data is exchanged. Each criterion states the OUTCOME tested; the minimum measurable specification is given in the Technical Baseline (Reference Guide, Ch. 3) (TB-01 to TB-14). Any product, platform or method that meets or exceeds the baseline is acceptable. Outcomes are tested by using the system (black-box); where documents are needed, vendors may choose any evidence option in Instructions 4B — internals and trade secrets are never required. DISCLAIMER: this is SECURITY CONFORMANCE TESTING of defined controls. Passing it is NOT equivalent to passing a vulnerability assessment and penetration test (VAPT) or a full cybersecurity assessment (TEC-14 only checks that an independent assessment exists). EXCEPTION HANDLING (TS3-01 to TS3-09): the EMR must not show a failed exchange as successful, must explain the error, allow correction, and leave exactly one correct referral on the SHR — inputs and expected results are in Test Data Section D (TD-D##).</t>
+          <t>Baseline technical safeguards that are REQUIRED before live patient data is exchanged. Each criterion states the outcome tested. The Technical Baseline (Reference Guide, Ch. 3) (TB-01 to TB-14) gives the minimum measurable specification. The vendor MAY use any product, platform or method that meets or exceeds the baseline. The Validator tests outcomes by using the system (black-box). Where documents are necessary, vendors MAY choose any evidence option in Instructions 4B. Vendors never need to give internals or trade secrets. Disclaimer: this is security conformance testing of defined controls. Passing it is not equivalent to passing a vulnerability assessment and penetration test (VAPT) or a full cybersecurity assessment. (TEC-14 only checks that an independent assessment exists.) Exception handling (TS3-01 to TS3-09): the EMR MUST NOT show a failed exchange as successful. The EMR MUST explain the error and allow correction. The EMR MUST leave exactly one correct referral on the SHR. Test Data Section D (TD-D##) gives the inputs and expected results.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="152.5" customHeight="1" s="125">
+    <row r="10" ht="179.5" customHeight="1" s="125">
       <c r="A10" s="172" t="inlineStr">
         <is>
           <t>TEC-01</t>
@@ -2526,16 +2526,20 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encrypt every endpoint used for the eReferral (EMR ↔ SHR, terminology server, user access) with TLS 1.2 or higher and a valid certificate; disable plain HTTP or redirect it to HTTPS; disable SSL, TLS 1.0/1.1 and weak cipher suites (TB-01, TB-02). Any web server, gateway, proxy or cloud service may be used.
-Purpose: Patient data cannot be read or changed while travelling over the network.
+          <t xml:space="preserve">Encrypt every endpoint that the eReferral uses (EMR ↔ SHR, terminology server, user access) with TLS 1.2 or higher and a valid certificate. Disable plain HTTP or redirect it to HTTPS. Disable SSL, TLS 1.0/1.1 and weak cipher suites (TB-01, TB-02). The vendor MAY use any web server, gateway, proxy or cloud service.
+Purpose: Patient data cannot be read or changed while it moves over the network.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. List every endpoint used.
-2. Validator (server-side) scans each endpoint with a TLS testing tool (e.g., testssl.sh, nmap ssl-enum-ciphers or an online TLS checker).
-3. Met only if EVERY endpoint uses https://, negotiates TLS 1.2 or 1.3 only, offers no cipher suite listed as not acceptable in TB-02, and has a valid, unexpired certificate matching the host name.
+          <t xml:space="preserve">1. List every endpoint that the system uses.
+2. Validator (server-side) scans each endpoint with a TLS testing tool (for example, testssl.sh, nmap ssl-enum-ciphers or an online TLS checker).
+3. Met only if every endpoint meets all four conditions:
+(a) it uses https://.
+(b) it negotiates TLS 1.2 or 1.3 only.
+(c) it offers no cipher suite that TB-02 lists as not acceptable.
+(d) it has a valid, unexpired certificate that matches the host name.
 </t>
         </is>
       </c>
@@ -2602,7 +2606,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="125.5" customHeight="1" s="125">
+    <row r="11" ht="139" customHeight="1" s="125">
       <c r="A11" s="172" t="inlineStr">
         <is>
           <t>TEC-02</t>
@@ -2615,19 +2619,19 @@
       </c>
       <c r="C11" s="172" t="inlineStr">
         <is>
-          <t>Each user has a unique account; no shared logins</t>
+          <t>Each user has a unique account (no shared logins)</t>
         </is>
       </c>
       <c r="D11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Require one account per user; no generic or shared accounts. Protect accounts per TB-05 (minimum password length, failed-attempt lock-out or throttling, no default passwords). Any identity method is acceptable (local accounts, LDAP / Active Directory, single sign-on, OpenID Connect).
+          <t xml:space="preserve">Require one account per user. Do not use generic or shared accounts. Protect accounts as TB-05 specifies (minimum password length, lock-out or throttling after failed attempts, no default passwords). The vendor MAY use any identity method (local accounts, LDAP / Active Directory, single sign-on, OpenID Connect).
 Purpose: Every action can be traced to a person.
 </t>
         </is>
       </c>
       <c r="E11" s="172" t="inlineStr">
         <is>
-          <t>Check that the system requires a unique account per user and that no generic/shared accounts are used for test referrals. Then try (a) a password shorter than the TB-05 minimum and (b) repeated failed log-ins. Met only if all three behave as TB-05 requires.</t>
+          <t>Check that the system requires a unique account for each user. Check that no generic or shared accounts are used for test referrals. Then try (a) a password shorter than the TB-05 minimum and (b) repeated failed log-ins. Met only if all three behave as TB-05 requires.</t>
         </is>
       </c>
       <c r="F11" s="172" t="inlineStr">
@@ -2712,14 +2716,14 @@
       <c r="D12" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Implement role-based access for referring clinician, receiving clinician, administrator and report viewer.
-Purpose: Staff only see the data they need.
+Purpose: Staff see only the data that they need.
 </t>
         </is>
       </c>
       <c r="E12" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Log in with each of the 4 roles and try one action outside the role. Count roles that behave correctly.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Log in with each of the 4 roles. For each role, try one action outside the role. Count the roles that behave correctly.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -3012,15 +3016,15 @@
       </c>
       <c r="D17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Log user, date/time and action for create, view, edit, send, receive, accept, decline, print, export and log-in events, with the fields required by TB-08. The storage format (database table, log file, FHIR AuditEvent, SIEM) is the vendor's choice.
-Purpose: Needed for accountability and privacy compliance.
+          <t xml:space="preserve">Log user, date/time and action for these events: create, view, edit, send, receive, accept, decline, print, export and log-in. Include the fields that TB-08 requires. The vendor MAY choose the storage format (database table, log file, FHIR AuditEvent, SIEM).
+Purpose: The audit trail is necessary for accountability and privacy compliance.
 </t>
         </is>
       </c>
       <c r="E17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform the 10 actions listed in the Notes (create, view, edit, send, receive, accept, decline, print, export, log-in). Count the actions found in the audit log with user and time.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Do the 10 actions listed in the Notes (create, view, edit, send, receive, accept, decline, print, export, log-in). Count the actions that the audit log shows with user and time.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -3613,14 +3617,14 @@
       </c>
       <c r="D28" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Log the user out, or lock the session and require re-authentication, after an idle period the facility can configure; the default must not exceed the TB-06 value.
+          <t xml:space="preserve">Log the user out, or lock the session and require re-authentication, after an idle period that the facility can configure. The default MUST NOT exceed the TB-06 value.
 Purpose: Unattended screens do not expose patient data.
 </t>
         </is>
       </c>
       <c r="E28" s="172" t="inlineStr">
         <is>
-          <t>Check the configured idle period (default per TB-06), then leave a session idle for that time. Met if the user is logged out or the session is locked and requires re-authentication.</t>
+          <t>Check the configured idle period (default as TB-06 specifies). Then leave a session idle for that time. Met if the user is logged out, or the session is locked and requires re-authentication.</t>
         </is>
       </c>
       <c r="F28" s="172" t="inlineStr">
@@ -3686,7 +3690,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="341.5" customHeight="1" s="125">
+    <row r="29" ht="382" customHeight="1" s="125">
       <c r="A29" s="172" t="inlineStr">
         <is>
           <t>TEC-07</t>
@@ -3704,25 +3708,30 @@
       </c>
       <c r="D29" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide backup and restore of data held only in the system — user accounts / credentials, roles, audit trail and configuration — meeting TB-09 (automated, encrypted, stored separately). The backup tool and location are the vendor's choice.
-Evidence options (vendor's choice — any ONE that proves compliance): (a) the full document / configuration; (b) a high-level or redacted version plus a signed attestation by an authorized officer that the control meets the referenced TB items; (c) independent certification or report (e.g., ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter); or (d) a view-only presentation (screen share or on site) recorded by the Validators as "sighted" with date, without keeping a copy. Source code, keys, credentials and internal network details are never required. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
-Purpose: Data that exists only in the system — not on the Shared Health Record — can be recovered after a failure.
+          <t xml:space="preserve">Provide backup and restore for the data that only the system holds: user accounts / credentials, roles, audit trail and configuration. Use a backup that meets TB-09 (automated, encrypted, stored separately). The vendor MAY choose the backup tool and location.
+Evidence options (the vendor MAY choose any one that proves compliance):
+(a) the full document / configuration.
+(b) a high-level or redacted version, plus a signed attestation by an authorized officer that the control meets the referenced TB items.
+(c) independent certification or report (for example, ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter).
+(d) a view-only presentation (screen share or on site). The Validators record it as "sighted" with the date and do not keep a copy.
+Source code, keys, credentials and internal network details are never necessary as evidence. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
+Purpose: Data that exists only in the system (not on the Shared Health Record) can be recovered after a failure.
 </t>
         </is>
       </c>
       <c r="E29" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Met if ANY one of the following shows that system-only data (user accounts, audit trail, configuration) is backed up per TB-09 and can be restored:
-(a) a live restore demonstration in the test environment;
-(b) a dated restore-test record (log or report) accepted by the Technical Lead;
-(c) a hosting / cloud-provider backup report plus a signed vendor attestation that system-only data is included and restores are tested.
+          <t xml:space="preserve">System-only data includes user accounts, audit trail and configuration. Met if any one option below shows a restorable TB-09 backup of system-only data:
+(a) a live restore demonstration in the test environment.
+(b) a dated restore-test record (log or report) that the Technical Lead accepts.
+(c) a hosting / cloud-provider backup report, plus a signed vendor attestation that the backup includes system-only data and that restores are tested.
 Record the evidence option used in Notes.
 </t>
         </is>
       </c>
       <c r="F29" s="172" t="inlineStr">
         <is>
-          <t>Restore demonstration, OR restore-test record, OR provider backup report + signed attestation</t>
+          <t>Restore demonstration, or restore-test record, or provider backup report + signed attestation</t>
         </is>
       </c>
       <c r="G29" s="172" t="inlineStr">
@@ -3783,7 +3792,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="368.5" customHeight="1" s="125">
+    <row r="30" ht="395.5" customHeight="1" s="125">
       <c r="A30" s="172" t="inlineStr">
         <is>
           <t>TEC-08</t>
@@ -3801,18 +3810,23 @@
       </c>
       <c r="D30" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encrypt personal and health data held by the system — database, stored files/attachments and backups — with AES-128 or stronger, keeping keys separate from the data (TB-03). Store passwords only as salted hashes using Argon2id, bcrypt, scrypt or PBKDF2 (TB-04). Any encryption layer is acceptable (full-disk/volume, database, file or field level).
-Evidence options (vendor's choice — any ONE that proves compliance): (a) the full document / configuration; (b) a high-level or redacted version plus a signed attestation by an authorized officer that the control meets the referenced TB items; (c) independent certification or report (e.g., ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter); or (d) a view-only presentation (screen share or on site) recorded by the Validators as "sighted" with date, without keeping a copy. Source code, keys, credentials and internal network details are never required. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
+          <t xml:space="preserve">Encrypt personal and health data that the system holds (database, stored files/attachments and backups) with AES-128 or stronger. Keep the keys separate from the data (TB-03). Store passwords only as salted hashes that use Argon2id, bcrypt, scrypt or PBKDF2 (TB-04). The vendor MAY use any encryption layer (full-disk/volume, database, file or field level).
+Evidence options (the vendor MAY choose any one that proves compliance):
+(a) the full document / configuration.
+(b) a high-level or redacted version, plus a signed attestation by an authorized officer that the control meets the referenced TB items.
+(c) independent certification or report (for example, ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter).
+(d) a view-only presentation (screen share or on site). The Validators record it as "sighted" with the date and do not keep a copy.
+Source code, keys, credentials and internal network details are never necessary as evidence. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
 Purpose: A stolen disk, database copy or backup does not expose patient data or passwords.
 </t>
         </is>
       </c>
       <c r="E30" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Met if compliance with BOTH TB-03 and TB-04 is shown by any accepted evidence option, e.g.:
-(a) view-only demonstration of the encryption setting and of the stored form of one TEST password;
-(b) configuration screenshots with key values masked;
-(c) cloud-provider encryption setting or independent certification covering encryption at rest, plus a signed attestation naming the password-hashing algorithm.
+          <t xml:space="preserve">Met if any accepted evidence option shows compliance with both TB-03 and TB-04. Examples of accepted options:
+(a) a view-only demonstration of the encryption setting and of the stored form of one test password.
+(b) configuration screenshots with key values masked.
+(c) a cloud-provider encryption setting or independent certification that covers encryption at rest, plus a signed attestation that names the password-hashing algorithm.
 Not Met if any evidence shows plain-text, reversible or MD5 / SHA-1 password storage, or no encryption at rest. Record the evidence option used in Notes.
 </t>
         </is>
@@ -3880,7 +3894,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="260.5" customHeight="1" s="125">
+    <row r="31" ht="287.5" customHeight="1" s="125">
       <c r="A31" s="172" t="inlineStr">
         <is>
           <t>TEC-09</t>
@@ -3898,20 +3912,20 @@
       </c>
       <c r="D31" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enforce authorisation on the SERVER side for every screen and API call: by role (TEC-03) and by facility (a user acts only for the facility/ies assigned). Reject guessed or changed record IDs that belong to another facility. Use generic log-in error messages and lock-out / throttling per TB-05.
-Purpose: Prevents the most common real-world breaches — staff or outsiders reading records they are not entitled to.
+          <t xml:space="preserve">Enforce authorisation on the server side for every screen and API call. Enforce it by role (TEC-03) and by facility (a user acts only for the facility or facilities assigned to that user). Reject guessed or changed record IDs that belong to another facility. Use generic log-in error messages, and lock-out / throttling as TB-05 specifies.
+Purpose: This prevents the most common real-world breaches: staff or outsiders who read records that they are not entitled to read.
 </t>
         </is>
       </c>
       <c r="E31" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use two test accounts: User A (referring clinician, Facility A) and User B (receiving clinician, Facility B), plus TD-D18 to TD-D21.
-1. Enter a wrong password for a valid user and for a non-existent user: messages must be identical; after the TB-05 limit the account is locked or throttled.
-2. As User A, try to open a referral addressed only to Facility C (list, search, direct link).
-3. Change the referral / patient ID in the URL or API call to one belonging to Facility C.
-4. As a non-administrator, open an administrator page by direct URL / API and try to change your own role.
+          <t xml:space="preserve">Use two test accounts and TD-D18 to TD-D21. User A is a referring clinician at Facility A. User B is a receiving clinician at Facility B.
+1. Enter a wrong password for a valid user and for a non-existent user. Check that the two messages are identical. Check that the account is locked or throttled after the TB-05 limit.
+2. As User A, try to open a referral that is addressed only to Facility C (list, search, direct link).
+3. Change the referral ID or patient ID in the URL or API call to an ID that belongs to Facility C.
+4. As a non-administrator, open an administrator page by direct URL / API. Then try to change your own role.
 5. Call the EMR's API without a valid session / token.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -3999,7 +4013,7 @@
       </c>
       <c r="C32" s="193" t="inlineStr">
         <is>
-          <t>Failed log-in: generic message (no user enumeration) and lock-out / throttling per TB-05 (TD-D18)</t>
+          <t>Failed log-in: generic message (no user enumeration) and lock-out / throttling as TB-05 specifies (TD-D18)</t>
         </is>
       </c>
       <c r="D32" s="195" t="inlineStr">
@@ -4049,7 +4063,7 @@
       </c>
       <c r="C33" s="193" t="inlineStr">
         <is>
-          <t>Cross-facility access blocked — referrals of another facility cannot be listed, searched or opened (TD-D19)</t>
+          <t>Cross-facility access blocked: referrals of another facility cannot be listed, searched or opened (TD-D19)</t>
         </is>
       </c>
       <c r="D33" s="195" t="inlineStr">
@@ -4103,7 +4117,7 @@
       </c>
       <c r="C34" s="193" t="inlineStr">
         <is>
-          <t>Direct object reference blocked — changing an ID in the URL / API does not reveal another facility's data (TD-D20)</t>
+          <t>Direct object reference blocked: a changed ID in the URL / API does not show the data of another facility (TD-D20)</t>
         </is>
       </c>
       <c r="D34" s="195" t="inlineStr">
@@ -4157,7 +4171,7 @@
       </c>
       <c r="C35" s="193" t="inlineStr">
         <is>
-          <t>No privilege escalation — admin functions unreachable by direct URL / API; users cannot change their own role (TD-D21)</t>
+          <t>No privilege escalation: admin functions cannot be reached by direct URL / API, and users cannot change their own role (TD-D21)</t>
         </is>
       </c>
       <c r="D35" s="195" t="inlineStr">
@@ -4248,7 +4262,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="152.5" customHeight="1" s="125">
+    <row r="37" ht="166" customHeight="1" s="125">
       <c r="A37" s="172" t="inlineStr">
         <is>
           <t>TEC-10</t>
@@ -4266,17 +4280,17 @@
       </c>
       <c r="D37" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invalidate the session on the server at log-out; refuse expired sessions and tokens; when an administrator deactivates an account, block new log-ins immediately and end its active sessions within the TB-12 limit.
-Purpose: Departed staff and stolen sessions cannot keep accessing patient data.
+          <t xml:space="preserve">Invalidate the session on the server at log-out. Refuse expired sessions and tokens. When an administrator deactivates an account, block new log-ins immediately. Also end the active sessions of that account within the TB-12 limit.
+Purpose: Former staff and stolen sessions cannot continue to access patient data.
 </t>
         </is>
       </c>
       <c r="E37" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Log in, copy the session (or note the page), log out, then press Back / replay the request: access must be refused.
-2. Wait past the idle / token expiry (TB-06 / TB-12) and repeat an action: re-authentication is required.
-3. Administrator deactivates a logged-in test user: the user cannot log in again, and the open session ends within the TB-12 limit.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">1. Log in, copy the session (or note the page) and log out. Then press Back / replay the request. Check that access is refused.
+2. Wait past the idle / token expiry (TB-06 / TB-12) and repeat an action. Check that the system asks for re-authentication.
+3. An administrator deactivates a logged-in test user. Check that the user cannot log in again. Check that the open session ends within the TB-12 limit.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -4414,7 +4428,7 @@
       </c>
       <c r="C39" s="193" t="inlineStr">
         <is>
-          <t>Expired session / token refused; re-authentication required</t>
+          <t>Expired session / token refused, and the system asks for re-authentication</t>
         </is>
       </c>
       <c r="D39" s="195" t="inlineStr">
@@ -4464,7 +4478,7 @@
       </c>
       <c r="C40" s="193" t="inlineStr">
         <is>
-          <t>Deactivated account: new log-in blocked immediately; active session ended within the TB-12 limit</t>
+          <t>Deactivated account: new log-in blocked immediately, and active session ended within the TB-12 limit</t>
         </is>
       </c>
       <c r="D40" s="195" t="inlineStr">
@@ -4514,12 +4528,12 @@
       </c>
       <c r="C41" s="172" t="inlineStr">
         <is>
-          <t>Error messages, client-side code and logs do not expose secrets, system internals or patient data beyond what the user may see</t>
+          <t>Error messages, client-side code and logs do not expose secrets, system internals or patient data beyond what the user has permission to see</t>
         </is>
       </c>
       <c r="D41" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Show users generic error messages (no stack traces, SQL, file paths or server versions); keep credentials, tokens and API keys out of browser / mobile code, URLs and browser storage (TB-07); keep full identifiers and clinical content out of application logs except where required by TB-08 audit (TB-13).
+          <t xml:space="preserve">Show users generic error messages (no stack traces, SQL, file paths or server versions). Keep credentials, tokens and API keys out of browser / mobile code, URLs and browser storage (TB-07). Keep full identifiers and clinical content out of application logs, except where the TB-08 audit requires them (TB-13).
 Purpose: Error screens and logs are a frequent source of data leaks.
 </t>
         </is>
@@ -4527,9 +4541,9 @@
       <c r="E41" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Trigger errors (TD-D03, a non-existent page, a broken request) and read the messages.
-2. Open the browser developer tools (or inspect the mobile app traffic) and look for secrets in source, URLs, local / session storage.
-3. Review a sample application log from the test session, OR accept a signed attestation with a redacted sample (Instructions 4B).
-Mark each sub-item (↳) below; Achieved is counted automatically.
+2. Open the browser developer tools (or inspect the mobile app traffic). Look for secrets in the source, URLs and local / session storage.
+3. Review a sample application log from the test session, or accept a signed attestation with a redacted sample (Instructions 4B).
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -4767,12 +4781,12 @@
       </c>
       <c r="C45" s="172" t="inlineStr">
         <is>
-          <t>The audit log cannot be altered through the application and records security events</t>
+          <t>The audit log cannot be changed through the application and records security events</t>
         </is>
       </c>
       <c r="D45" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make audit entries append-only for every application role, including administrators; log failed log-ins, role / permission changes and account deactivation; restrict viewing / export of the audit log to an authorised role (TB-08).
+          <t xml:space="preserve">Make audit entries append-only for every application role, including administrators. Log failed log-ins, role / permission changes and account deactivation. Restrict audit log viewing / export to an authorised role (TB-08).
 Purpose: An audit trail that can be edited proves nothing.
 </t>
         </is>
@@ -4780,9 +4794,9 @@
       <c r="E45" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. As an ordinary user and as an administrator, try to edit or delete an audit entry through the application.
-2. Check that the failed log-ins (TEC-09.1), the role change attempt (TEC-09.4) and the deactivation (TEC-10.3) appear in the log.
+2. Check that the log shows the failed log-ins (TEC-09.1), the role change attempt (TEC-09.4) and the deactivation (TEC-10.3).
 3. Try to open the audit log with a non-authorised role.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -5075,16 +5089,16 @@
       </c>
       <c r="D50" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validate the certificate of the SHR / terminology server on every connection (no 'trust all certificates' setting). If the EMR exposes its own API to the internet, apply rate limiting or equivalent abuse controls.
-Purpose: Prevents interception (man-in-the-middle) and denial-of-service by request flooding.
+          <t xml:space="preserve">Verify the certificate of the SHR / terminology server on every connection (no 'trust all certificates' setting). If the EMR exposes its own API to the internet, apply rate limiting or equivalent abuse controls.
+Purpose: This prevents interception (man-in-the-middle) and denial-of-service by request flooding.
 </t>
         </is>
       </c>
       <c r="E50" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D22: the DOH provides a sandbox endpoint with an invalid / expired / untrusted certificate; point the EMR to it. Met if the EMR refuses to connect (N/A with reason if the DOH has not provisioned the endpoint).
-2. If the EMR exposes an internet-facing API: send repeated requests (within the agreed test limit) and confirm throttling or a documented control. N/A if no API is exposed.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">1. TD-D22: the DOH provides a sandbox endpoint with an invalid / expired / untrusted certificate. Configure the EMR to connect to it. Met if the EMR refuses to connect. If the DOH did not provision the endpoint, mark N/A with the reason.
+2. If the EMR exposes an internet-facing API, send repeated requests (within the agreed test limit). Confirm throttling or a documented control. N/A if the EMR exposes no API.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -5222,7 +5236,7 @@
       </c>
       <c r="C52" s="193" t="inlineStr">
         <is>
-          <t>Rate limiting / abuse control on any internet-facing API exposed by the EMR (N/A if none)</t>
+          <t>Rate limiting / abuse control on any internet-facing API that the EMR exposes (N/A if none)</t>
         </is>
       </c>
       <c r="D52" s="195" t="inlineStr">
@@ -5259,7 +5273,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="206.5" customHeight="1" s="125">
+    <row r="53" ht="220" customHeight="1" s="125">
       <c r="A53" s="172" t="inlineStr">
         <is>
           <t>TEC-14</t>
@@ -5277,14 +5291,14 @@
       </c>
       <c r="D53" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide evidence of a vulnerability assessment and penetration test or an authenticated vulnerability scan of the version under test (or the same major version) done within the last 12 months by an independent party or a separate security team (TB-14), with critical / high findings fixed or covered by a remediation plan accepted by the Technical Lead. Evidence options per Instructions 4B (e.g., executive summary + signed attestation).
-Purpose: Black-box conformance testing cannot replace a security assessment; this checks one was done.
+          <t xml:space="preserve">Provide evidence of a security assessment of the version under test (or the same major version). The assessment is a vulnerability assessment and penetration test, or an authenticated vulnerability scan. An independent party or a separate security team did it within the last 12 months (TB-14). Critical / high findings are fixed or covered by a remediation plan that the Technical Lead accepts. Evidence options are as Instructions 4B specifies (for example, executive summary + signed attestation).
+Purpose: Black-box conformance testing cannot replace a security assessment. This criterion checks that one was done.
 </t>
         </is>
       </c>
       <c r="E53" s="172" t="inlineStr">
         <is>
-          <t>Check the date, scope (product + version), assessor independence and the status of critical / high findings. Met only if all four are acceptable. This criterion does NOT make this validation a security assessment (see disclaimer above).</t>
+          <t>Check the date, the scope (product + version), the independence of the assessor and the status of critical / high findings. Met only if all four are acceptable. This criterion does not make this validation a security assessment (see the disclaimer above).</t>
         </is>
       </c>
       <c r="F53" s="172" t="inlineStr">
@@ -5350,7 +5364,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="247" customHeight="1" s="125">
+    <row r="54" ht="314.5" customHeight="1" s="125">
       <c r="A54" s="172" t="inlineStr">
         <is>
           <t>TS3-01</t>
@@ -5363,23 +5377,28 @@
       </c>
       <c r="C54" s="172" t="inlineStr">
         <is>
-          <t>A referral missing an element the IG makes mandatory is not shown as sent, the reason is shown to the user, and the corrected referral is accepted</t>
+          <t>A referral without an element that the IG makes mandatory is not shown as sent, the reason is shown to the user, and the corrected referral is accepted</t>
         </is>
       </c>
       <c r="D54" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent sending, OR handle the SHR rejection (HTTP 4xx with OperationOutcome) of a referral that lacks an element with minimum cardinality ≥ 1 in the PHeReF / PH Core profiles (see FHIR Traceability (Reference Guide, Ch. 5), column 'Cardinality'). Show the user which item is missing, keep the referral as not sent, and allow correction and resend.
-Purpose: A referral that the SHR refused must never look 'sent' to the referring clinician.
+          <t xml:space="preserve">This applies to a referral that lacks an element with minimum cardinality ≥ 1 in the PHeReF / PH Core profiles. These elements are in FHIR Traceability (Reference Guide, Ch. 5), column 'Cardinality'. For such a referral, prevent sending, or handle the SHR rejection (HTTP 4xx with OperationOutcome). Show the user which item is missing. Keep the referral as not sent, and allow correction and resend.
+Purpose: A referral that the SHR refused MUST NOT look 'sent' to the referring clinician.
 </t>
         </is>
       </c>
       <c r="E54" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Use TD-D01 (patient birth date left blank) and TD-D02 (receiving facility not selected).
-2. For each sub-item: try to submit. Met if EITHER the EMR blocks it before sending with a clear message, OR the SHR rejects it and the EMR shows the rejection in understandable terms and keeps the referral as NOT sent.
-3. Correct the value and resend; confirm on the SHR that exactly one accepted referral exists.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. For each sub-item, try to submit. Met if either of these occurs:
+(a) the EMR blocks it before sending, with a clear message.
+(b) the SHR rejects it, and the EMR shows the rejection in understandable terms and keeps the referral as not sent.
+3. Correct the value and resend. On the SHR, check that exactly one accepted referral exists.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -5467,7 +5486,7 @@
       </c>
       <c r="C55" s="193" t="inlineStr">
         <is>
-          <t>Missing Patient.birthDate (1..1) — blocked or rejection shown; referral not marked sent (TD-D01)</t>
+          <t>Missing Patient.birthDate (1..1): blocked or rejection shown, and referral not marked sent (TD-D01)</t>
         </is>
       </c>
       <c r="D55" s="195" t="inlineStr">
@@ -5521,7 +5540,7 @@
       </c>
       <c r="C56" s="193" t="inlineStr">
         <is>
-          <t>Missing receiving facility (ServiceRequest.performer) — blocked or rejection shown (TD-D02)</t>
+          <t>Missing receiving facility (ServiceRequest.performer): blocked or rejection shown (TD-D02)</t>
         </is>
       </c>
       <c r="D56" s="195" t="inlineStr">
@@ -5616,7 +5635,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="193" customHeight="1" s="125">
+    <row r="58" ht="247" customHeight="1" s="125">
       <c r="A58" s="172" t="inlineStr">
         <is>
           <t>TS3-02</t>
@@ -5629,22 +5648,27 @@
       </c>
       <c r="C58" s="172" t="inlineStr">
         <is>
-          <t>Malformed values (wrong data type or format) are prevented or the SHR rejection is handled without data loss</t>
+          <t>Malformed values (wrong data type or format) are prevented, or the SHR rejection is handled without data loss</t>
         </is>
       </c>
       <c r="D58" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validate data types and formats before sending (dates in ISO 8601, numeric vital signs with UCUM units, identifier formats per PH Core), OR handle the SHR rejection clearly. Entered data must not be lost when an error occurs.
+          <t xml:space="preserve">Validate data types and formats before sending, or handle the SHR rejection clearly. Examples of formats: dates in ISO 8601, numeric vital signs with UCUM units, identifier formats as PH Core specifies. The EMR MUST NOT lose entered data when an error occurs.
 Purpose: Bad formats are caught early and do not reach other facilities.
 </t>
         </is>
       </c>
       <c r="E58" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Use TD-D03 (impossible date, e.g., 2026-02-30), TD-D04 (non-numeric heart rate) and TD-D05 (birth date in the future).
-2. Met per sub-item if the system blocks the value OR shows the SHR rejection clearly, and the rest of the entered referral is kept for correction.
-Mark each sub-item (↳) below; Achieved is counted automatically.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Use TD-D03 (impossible date, for example 2026-02-30), TD-D04 (non-numeric heart rate) and TD-D05 (birth date in the future).
+2. Met per sub-item if both conditions are true:
+(a) the system blocks the value, or shows the SHR rejection clearly.
+(b) the system keeps the rest of the entered referral for correction.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -5732,7 +5756,7 @@
       </c>
       <c r="C59" s="193" t="inlineStr">
         <is>
-          <t>Impossible date (TD-D03) — prevented or rejection handled</t>
+          <t>Impossible date (TD-D03): prevented or rejection handled</t>
         </is>
       </c>
       <c r="D59" s="195" t="inlineStr">
@@ -5782,7 +5806,7 @@
       </c>
       <c r="C60" s="193" t="inlineStr">
         <is>
-          <t>Non-numeric vital-sign value (TD-D04) — prevented or rejection handled</t>
+          <t>Non-numeric vital-sign value (TD-D04): prevented or rejection handled</t>
         </is>
       </c>
       <c r="D60" s="195" t="inlineStr">
@@ -5832,7 +5856,7 @@
       </c>
       <c r="C61" s="193" t="inlineStr">
         <is>
-          <t>Birth date in the future (TD-D05) — prevented or rejection handled</t>
+          <t>Birth date in the future (TD-D05): prevented or rejection handled</t>
         </is>
       </c>
       <c r="D61" s="195" t="inlineStr">
@@ -5869,7 +5893,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="179.5" customHeight="1" s="125">
+    <row r="62" ht="206.5" customHeight="1" s="125">
       <c r="A62" s="172" t="inlineStr">
         <is>
           <t>TS3-03</t>
@@ -5882,12 +5906,12 @@
       </c>
       <c r="C62" s="172" t="inlineStr">
         <is>
-          <t>References to a facility, practitioner or patient that does not exist are prevented or the rejection is handled</t>
+          <t>References to a facility, practitioner or patient that does not exist are prevented, or the rejection is handled</t>
         </is>
       </c>
       <c r="D62" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve every reference before sending — facilities from the NHFR (TS0-06), practitioners from the registered list — OR handle the SHR rejection of an unresolvable reference clearly.
+          <t xml:space="preserve">Resolve every reference before sending, or handle clearly the SHR rejection of a reference that cannot be resolved. Resolve facilities from the NHFR (TS0-06) and practitioners from the registered list.
 Purpose: A referral cannot be addressed to a facility that does not exist.
 </t>
         </is>
@@ -5895,9 +5919,12 @@
       <c r="E62" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Use TD-D06 (NHFR code not in the registry) and TD-D07 (practitioner not registered in the sandbox).
-2. Met per sub-item if the system blocks it OR shows the SHR rejection clearly and keeps the referral as not sent.
-Mark each sub-item (↳) below; Achieved is counted automatically.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Met per sub-item if the system blocks it, or shows the SHR rejection clearly and keeps the referral as not sent.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -5985,7 +6012,7 @@
       </c>
       <c r="C63" s="193" t="inlineStr">
         <is>
-          <t>Unknown receiving facility NHFR code (TD-D06) — prevented or handled</t>
+          <t>Unknown receiving facility NHFR code (TD-D06): prevented or handled</t>
         </is>
       </c>
       <c r="D63" s="195" t="inlineStr">
@@ -6035,7 +6062,7 @@
       </c>
       <c r="C64" s="193" t="inlineStr">
         <is>
-          <t>Unregistered practitioner as requester (TD-D07) — prevented or handled</t>
+          <t>Unregistered practitioner as requester (TD-D07): prevented or handled</t>
         </is>
       </c>
       <c r="D64" s="195" t="inlineStr">
@@ -6072,7 +6099,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" ht="233.5" customHeight="1" s="125">
+    <row r="65" ht="274" customHeight="1" s="125">
       <c r="A65" s="172" t="inlineStr">
         <is>
           <t>TS3-04</t>
@@ -6085,23 +6112,31 @@
       </c>
       <c r="C65" s="172" t="inlineStr">
         <is>
-          <t>Submitting the same referral twice (double click, resend after timeout, re-opened draft) leaves only ONE referral on the SHR</t>
+          <t>Submitting the same referral twice (double click, resend after timeout, re-opened draft) leaves only one referral on the SHR</t>
         </is>
       </c>
       <c r="D65" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make sending idempotent — e.g., disable the Send action while waiting, give each referral a business identifier and use conditional create (If-None-Exist) or a transaction Bundle with conditional entries, or check the SHR before resending. The method is the vendor's choice.
+          <t xml:space="preserve">Make sending idempotent. Examples:
+(a) disable the Send action while waiting.
+(b) give each referral a business identifier, and use conditional create (If-None-Exist) or a transaction Bundle with conditional entries.
+(c) check the SHR before resending.
+The vendor MAY choose the method.
 Purpose: Duplicate referrals distort Level 3 counts and make the receiving facility prepare twice.
 </t>
         </is>
       </c>
       <c r="E65" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D08: click Send twice quickly. 2. TD-D09: after a send, use the system's own resend / retry function for the same referral.
+          <t xml:space="preserve">1. TD-D08: click Send twice quickly.
+2. TD-D09: after a send, use the resend / retry function of the system for the same referral.
 3. Validator (server-side) searches the SHR (ServiceRequest by patient and authored date, or by business identifier).
-Met per sub-item only if exactly ONE ServiceRequest and ONE Task exist for that referral.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Met per sub-item only if exactly one ServiceRequest and one Task exist for that referral.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -6189,7 +6224,7 @@
       </c>
       <c r="C66" s="193" t="inlineStr">
         <is>
-          <t>Double Send (TD-D08) — exactly one ServiceRequest and one Task on the SHR</t>
+          <t>Double Send (TD-D08): exactly one ServiceRequest and one Task on the SHR</t>
         </is>
       </c>
       <c r="D66" s="195" t="inlineStr">
@@ -6243,7 +6278,7 @@
       </c>
       <c r="C67" s="193" t="inlineStr">
         <is>
-          <t>Resend / retry of an already accepted referral (TD-D09) — no second referral created</t>
+          <t>Resend / retry of an already accepted referral (TD-D09): no second referral created</t>
         </is>
       </c>
       <c r="D67" s="195" t="inlineStr">
@@ -6284,7 +6319,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="247" customHeight="1" s="125">
+    <row r="68" ht="314.5" customHeight="1" s="125">
       <c r="A68" s="172" t="inlineStr">
         <is>
           <t>TS3-05</t>
@@ -6302,18 +6337,23 @@
       </c>
       <c r="D68" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queue referrals made during connection loss and resend automatically, OR provide a documented manual fallback (user manual L1-02.5). After recovery the referral must arrive once, with the original date/time referred (absorbs Rev 6 TEC-06).
+          <t xml:space="preserve">Queue referrals made during connection loss and resend them automatically, or provide a documented manual fallback (user manual L1-02.5). After recovery, the referral MUST arrive once, with the original date/time referred (absorbs Rev 6 TEC-06).
 Purpose: Referrals continue during outages without loss or duplication.
 </t>
         </is>
       </c>
       <c r="E68" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D10: disconnect the network, create and send a referral; reconnect.
-2. TD-D11: interrupt the connection while a send is in progress (e.g., disable the network adapter immediately after Send).
-3. Met per sub-item if, after recovery, exactly one copy is on the SHR with the original authoredOn, and the user was told the status (queued / failed / sent).
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. TD-D10: disconnect the network. Create and send a referral. Then reconnect.
+2. TD-D11: interrupt the connection while a send is in progress (for example, disable the network adapter immediately after Send).
+3. Met per sub-item if both conditions are true after recovery:
+(a) exactly one copy is on the SHR with the original authoredOn.
+(b) the user was told the status (queued / failed / sent).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -6401,7 +6441,7 @@
       </c>
       <c r="C69" s="193" t="inlineStr">
         <is>
-          <t>Offline creation (TD-D10) — queued or documented fallback followed; user sees status</t>
+          <t>Offline creation (TD-D10): queued or documented fallback followed, and user sees status</t>
         </is>
       </c>
       <c r="D69" s="195" t="inlineStr">
@@ -6455,7 +6495,7 @@
       </c>
       <c r="C70" s="193" t="inlineStr">
         <is>
-          <t>Interruption mid-send (TD-D11) — no loss; exactly one copy after recovery</t>
+          <t>Interruption mid-send (TD-D11): no loss, and exactly one copy after recovery</t>
         </is>
       </c>
       <c r="D70" s="195" t="inlineStr">
@@ -6546,7 +6586,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="220" customHeight="1" s="125">
+    <row r="72" ht="260.5" customHeight="1" s="125">
       <c r="A72" s="172" t="inlineStr">
         <is>
           <t>TS3-06</t>
@@ -6564,18 +6604,21 @@
       </c>
       <c r="D72" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send the referral so that it succeeds or fails as a whole — e.g., a FHIR transaction Bundle (all-or-nothing) as in the IG example (ExampleERefSubmissionBundle), or compensating clean-up when resources are sent one by one. Report failure to the user.
+          <t xml:space="preserve">Send the referral so that it succeeds or fails as a whole. Examples: a FHIR transaction Bundle (all-or-nothing) as in the IG example (ExampleERefSubmissionBundle), or compensating clean-up when resources are sent one by one. Report failure to the user.
 Purpose: A ServiceRequest without its Task, Patient or clinical data is unusable for the receiving facility.
 </t>
         </is>
       </c>
       <c r="E72" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D12: include one invalid resource in the referral (e.g., an Observation with a code outside LOINC, prepared with the developer).
+          <t xml:space="preserve">1. TD-D12: include one invalid resource in the referral (for example, an Observation with a code outside LOINC, prepared with the developer).
 2. Submit. Validator (server-side) checks the SHR.
 Met per sub-item if no ServiceRequest / Task / partial resources from that attempt remain, and the EMR shows the failure.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -6717,7 +6760,7 @@
       </c>
       <c r="C74" s="193" t="inlineStr">
         <is>
-          <t>EMR does not show the referral as sent; the user can correct and resend</t>
+          <t>EMR does not show the referral as sent, and the user can correct and resend</t>
         </is>
       </c>
       <c r="D74" s="195" t="inlineStr">
@@ -6758,7 +6801,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="206.5" customHeight="1" s="125">
+    <row r="75" ht="247" customHeight="1" s="125">
       <c r="A75" s="172" t="inlineStr">
         <is>
           <t>TS3-07</t>
@@ -6776,18 +6819,23 @@
       </c>
       <c r="D75" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">When a look-up service is unreachable, use a validated cached copy (scheduled sync — see Terminology &amp; Registry Sources, Reference Guide Ch. 4) OR block the coded field with a clear message. Never substitute free text or locally invented codes for a bound element.
-Purpose: An outage of a national service must not corrupt the data exchanged.
+          <t xml:space="preserve">When a look-up service is unreachable, use a validated cached copy, or block the coded field with a clear message. The cached copy comes from a scheduled sync (see Terminology &amp; Registry Sources, Reference Guide Ch. 4). Never substitute free text or locally invented codes for a bound element.
+Purpose: An outage of a national service MUST NOT corrupt the exchanged data.
 </t>
         </is>
       </c>
       <c r="E75" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D13: the DOH makes the terminology server unreachable for the test account (or the developer points the EMR to a dead endpoint).
-2. TD-D14: same for the NHFR / facility list.
-3. Met per sub-item if the EMR uses a valid cached value set OR blocks with a clear message, and any code sent is valid (TS0 check on the SHR).
-Mark each sub-item (↳) below; Achieved is counted automatically.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. TD-D13: the DOH makes the terminology server unreachable for the test account (or the developer configures the EMR to use a dead endpoint).
+2. TD-D14: do the same for the NHFR / facility list.
+3. Met per sub-item if both conditions are true:
+(a) the EMR uses a valid cached value set, or blocks with a clear message.
+(b) any code sent is valid (TS0 check on the SHR).
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -6875,7 +6923,7 @@
       </c>
       <c r="C76" s="193" t="inlineStr">
         <is>
-          <t>Terminology server unavailable (TD-D13) — cached valid codes or clear block; no invented codes</t>
+          <t>Terminology server unavailable (TD-D13): cached valid codes or clear block, and no invented codes</t>
         </is>
       </c>
       <c r="D76" s="195" t="inlineStr">
@@ -6925,7 +6973,7 @@
       </c>
       <c r="C77" s="193" t="inlineStr">
         <is>
-          <t>Facility registry unavailable (TD-D14) — cached NHFR list or clear block; no free-typed facility</t>
+          <t>Facility registry unavailable (TD-D14): cached NHFR list or clear block, and no free-typed facility</t>
         </is>
       </c>
       <c r="D77" s="195" t="inlineStr">
@@ -6962,7 +7010,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="179.5" customHeight="1" s="125">
+    <row r="78" ht="233.5" customHeight="1" s="125">
       <c r="A78" s="172" t="inlineStr">
         <is>
           <t>TS3-08</t>
@@ -6980,7 +7028,7 @@
       </c>
       <c r="D78" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detect HTTP 401 / 403 from the SHR, tell the user (or administrator) that the connection credential failed, keep the referral as not sent / queued, and never display tokens, passwords or keys in messages or logs (TB-07, TB-13).
+          <t xml:space="preserve">Detect HTTP 401 / 403 from the SHR. Tell the user (or administrator) that the connection credential failed. Keep the referral as not sent / queued. Never show tokens, passwords or keys in messages or logs (TB-07, TB-13).
 Purpose: Expired credentials are a common cause of silent referral loss.
 </t>
         </is>
@@ -6988,8 +7036,15 @@
       <c r="E78" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">TD-D15: the DOH revokes or expires the system credential of the test EMR (or the developer configures an invalid one). Send a referral.
-Met only if the user sees an understandable failure, the referral remains not sent / queued, it is sent after the credential is restored, and no secret is shown.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Met only if all these conditions are true:
+(a) the user sees an understandable failure.
+(b) the referral stays not sent / queued.
+(c) the referral is sent after the credential is restored.
+(d) no secret is shown.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -7056,7 +7111,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="193" customHeight="1" s="125">
+    <row r="79" ht="233.5" customHeight="1" s="125">
       <c r="A79" s="172" t="inlineStr">
         <is>
           <t>TS3-09</t>
@@ -7074,18 +7129,21 @@
       </c>
       <c r="D79" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">When the SHR is unreachable, show the user that the incoming list may be out of date; after recovery, retrieve every referral addressed to the facility. If the same notification or resource is delivered twice, show the referral once (match by resource ID / business identifier).
+          <t xml:space="preserve">When the SHR is unreachable, show the user that the incoming list can be out of date. After recovery, retrieve every referral addressed to the facility. If the same notification or resource arrives twice, show the referral once (match by resource ID / business identifier).
 Purpose: No incoming referral is lost or duplicated at the receiving facility.
 </t>
         </is>
       </c>
       <c r="E79" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. TD-D16: make the SHR unreachable from the receiving EMR; submit two referrals from the referring side; restore.
-2. TD-D17: re-deliver / re-read the same referral (e.g., replay the notification or force a second poll).
+          <t xml:space="preserve">1. TD-D16: make the SHR unreachable from the receiving EMR. Submit two referrals from the referring side. Then restore the connection.
+2. TD-D17: re-deliver / re-read the same referral (for example, replay the notification or force a second poll).
 Met per sub-item as described.
-Mark each sub-item (↳) below; Achieved is counted automatically.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -7273,7 +7331,7 @@
       </c>
       <c r="C82" s="193" t="inlineStr">
         <is>
-          <t>Duplicate delivery (TD-D17) — referral listed once only</t>
+          <t>Duplicate delivery (TD-D17): referral listed once only</t>
         </is>
       </c>
       <c r="D82" s="195" t="inlineStr">
@@ -7369,7 +7427,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7418,7 +7476,7 @@
     <row r="2" ht="48" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>Reports must contain the required features and AGGREGATED DATA must be complete. Completeness is checked with the 10 known referrals in Test Data Section B — the aggregated figures must match the expected numbers.</t>
+          <t>Reports MUST contain the REQUIRED features. Aggregated data MUST be complete. The Validator checks completeness with the 10 known referrals in Test Data Section B. The aggregated figures MUST match the expected numbers.</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7502,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -7644,15 +7702,15 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide a printable referral form that includes all TS1 data elements. Layout and section order are the vendor's choice.
+          <t xml:space="preserve">Provide a printable referral form that includes all TS1 data elements. The vendor MAY choose the layout and section order.
 Purpose: A paper copy can go with the patient if needed.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Print the Test Data referral and compare each form section with the Test Data sheet. A section is Met only if every field in it is printed correctly; write any missing field in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Print the Test Data referral. Compare each form section with the Test Data sheet. A section is Met only if every field in it is printed correctly. Write any missing field in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -7740,7 +7798,7 @@
       </c>
       <c r="C11" s="193" t="inlineStr">
         <is>
-          <t>Facility details — referring and receiving facility names, NHFR codes, addresses, HCPN (TS1-01, TS1-02)</t>
+          <t>Facility details: referring and receiving facility names, NHFR codes, addresses, HCPN (TS1-01, TS1-02)</t>
         </is>
       </c>
       <c r="D11" s="195" t="inlineStr">
@@ -7790,7 +7848,7 @@
       </c>
       <c r="C12" s="193" t="inlineStr">
         <is>
-          <t>Patient details — name, PhilSys, PhilHealth, birth date / age, sex, civil status, address, contact, PWD, accompanying person (TS1-04, TS1-05)</t>
+          <t>Patient details: name, PhilSys, PhilHealth, birth date / age, sex, civil status, address, contact, PWD, accompanying person (TS1-04, TS1-05)</t>
         </is>
       </c>
       <c r="D12" s="195" t="inlineStr">
@@ -7840,7 +7898,7 @@
       </c>
       <c r="C13" s="193" t="inlineStr">
         <is>
-          <t>Referral details — date of referral, referral category, priority, reason for referral (TS1-06)</t>
+          <t>Referral details: date of referral, referral category, priority, reason for referral (TS1-06)</t>
         </is>
       </c>
       <c r="D13" s="195" t="inlineStr">
@@ -7890,7 +7948,7 @@
       </c>
       <c r="C14" s="193" t="inlineStr">
         <is>
-          <t>Clinical information — chief complaint, working impression, clinical history, vital signs, lab attachment noted, treatment given (TS1-07 to TS1-10)</t>
+          <t>Clinical information: chief complaint, working impression, clinical history, vital signs, lab attachment noted, treatment given (TS1-07 to TS1-10)</t>
         </is>
       </c>
       <c r="D14" s="195" t="inlineStr">
@@ -7940,7 +7998,7 @@
       </c>
       <c r="C15" s="193" t="inlineStr">
         <is>
-          <t>Practitioners and signature — referring practitioner and role, care navigator, signature with date / time (TS1-03, TS1-11)</t>
+          <t>Practitioners and signature: referring practitioner and role, care navigator, signature with date / time (TS1-03, TS1-11)</t>
         </is>
       </c>
       <c r="D15" s="195" t="inlineStr">
@@ -7990,7 +8048,7 @@
       </c>
       <c r="C16" s="193" t="inlineStr">
         <is>
-          <t>Referral status — current status and receiving facility response (TS1-12, TS2-11)</t>
+          <t>Referral status: current status and receiving facility response (TS1-12, TS2-11)</t>
         </is>
       </c>
       <c r="D16" s="195" t="inlineStr">
@@ -8045,15 +8103,15 @@
       </c>
       <c r="D17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide a referral linelist with the 6 required columns / filters.
+          <t xml:space="preserve">Provide a referral linelist with the 6 columns / filters listed below.
 Purpose: The linelist has all the columns the DOH needs.
 </t>
         </is>
       </c>
       <c r="E17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the required columns/filters present.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the columns / filters below that are present.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -8453,7 +8511,7 @@
       </c>
       <c r="E24" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compare the linelist count with the Expected value "Total referrals in linelist" in Test Data. All-or-nothing.
+          <t xml:space="preserve">Compare the linelist count with the Expected value "Total referrals in linelist" in Test Data. Scoring is all-or-nothing.
 Calculation rule: IND-01 (Reference Guide, Ch. 6), IND-02.
 </t>
         </is>
@@ -8547,7 +8605,7 @@
       <c r="E25" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Enter the system values in Test Data column C. Count the 3 values that show MATCH.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-05.
 </t>
         </is>
@@ -8799,7 +8857,7 @@
       <c r="E29" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the 2 values that show MATCH in Test Data.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-05.
 </t>
         </is>
@@ -9001,7 +9059,7 @@
       <c r="E32" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the 4 reason values that show MATCH in Test Data.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-06.
 </t>
         </is>
@@ -9303,7 +9361,7 @@
       <c r="E37" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the 4 ownership values that show MATCH in Test Data.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-07.
 </t>
         </is>
@@ -9492,7 +9550,7 @@
       </c>
       <c r="C40" s="193" t="inlineStr">
         <is>
-          <t>Outgoing — government referring facility match</t>
+          <t>Outgoing: government referring facility match</t>
         </is>
       </c>
       <c r="D40" s="195" t="inlineStr">
@@ -9542,7 +9600,7 @@
       </c>
       <c r="C41" s="193" t="inlineStr">
         <is>
-          <t>Outgoing — private referring facility match</t>
+          <t>Outgoing: private referring facility match</t>
         </is>
       </c>
       <c r="D41" s="195" t="inlineStr">
@@ -9605,7 +9663,7 @@
       <c r="E42" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the 5 capability values that show MATCH in Test Data.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-07.
 </t>
         </is>
@@ -10049,7 +10107,7 @@
       </c>
       <c r="E49" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add up the linelist by direction; Met only if it equals the aggregate report totals.
+          <t xml:space="preserve">Calculate the linelist totals by direction. Met only if they equal the aggregate report totals.
 Calculation rule: IND-09.
 </t>
         </is>
@@ -10135,14 +10193,14 @@
       </c>
       <c r="D50" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restrict dashboard viewers to de-identified, aggregated data — no names or IDs in views or exports.
+          <t xml:space="preserve">Restrict dashboard viewers to de-identified, aggregated data, with no names or IDs in views or exports.
 Purpose: Monitoring does not expose individual patients.
 </t>
         </is>
       </c>
       <c r="E50" s="172" t="inlineStr">
         <is>
-          <t>Log in as dashboard viewer; Met if no patient-identifying data can be seen or exported.</t>
+          <t>Log in as a dashboard viewer. Met if no patient-identifying data can be seen or exported.</t>
         </is>
       </c>
       <c r="F50" s="172" t="inlineStr">
@@ -10221,24 +10279,24 @@
       </c>
       <c r="C51" s="172" t="inlineStr">
         <is>
-          <t>New referral appears on the receiving facility's list without manual refresh — time limit deferred (for information)</t>
+          <t>New referral appears on the receiving facility's list without manual refresh (time limit deferred, for information)</t>
         </is>
       </c>
       <c r="D51" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refresh incoming referral lists automatically (polling, push or IOL notification — vendor's choice) without manual refresh. A time limit will be set after the consultant's recommendation.
+          <t xml:space="preserve">Refresh incoming referral lists automatically, without manual refresh. The vendor MAY choose polling, push or IOL notification. A time limit will be set after the consultant's recommendation.
 Purpose: Staff see urgent referrals without pressing F5.
 </t>
         </is>
       </c>
       <c r="E51" s="172" t="inlineStr">
         <is>
-          <t>Submit a referral and observe whether it appears without refreshing; record the observed time in Notes (for information). Not scored until a time limit is set.</t>
+          <t>Submit a referral. Observe whether it appears without refreshing. Record the observed time in Notes (for information). Not scored until a time limit is set.</t>
         </is>
       </c>
       <c r="F51" s="172" t="inlineStr">
         <is>
-          <t>Screen recording (optional)</t>
+          <t>Screen recording (OPTIONAL)</t>
         </is>
       </c>
       <c r="G51" s="172" t="inlineStr">
@@ -10324,8 +10382,8 @@
       </c>
       <c r="E52" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit 3 referrals; count the ones that trigger a notification automatically.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Submit 3 referrals. Count the referrals that trigger a notification automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -10575,8 +10633,8 @@
       </c>
       <c r="E56" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export the linelist; Met if the file opens and matches the screen.
-Totals reconciliation of exports is checked in L3-21.
+          <t xml:space="preserve">Export the linelist. Met if the file opens and matches the screen.
+L3-21 checks the reconciliation of export totals.
 </t>
         </is>
       </c>
@@ -10669,7 +10727,7 @@
       <c r="E57" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the disaggregations available.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -10963,14 +11021,14 @@
       <c r="D62" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count and rank referrals by working impression / diagnosis (ICD-10 coded) for the selected period.
-Purpose: Shows which conditions are driving referrals, for planning and capacity building.
+Purpose: Shows which conditions drive referrals, for planning and capacity building.
 </t>
         </is>
       </c>
       <c r="E62" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter the system values in Test Data column C (rows "Morbidity rank 1–4"). Count the 4 morbidity values that show MATCH; the ranking must follow the counts.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Enter the system values in Test Data column C (rows "Morbidity rank 1–4"). Count the 4 morbidity values that show MATCH. The ranking MUST follow the counts.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 Calculation rule: IND-10.
 </t>
         </is>
@@ -11059,7 +11117,7 @@
       </c>
       <c r="C63" s="193" t="inlineStr">
         <is>
-          <t>Rank 1 — J18.9 Pneumonia, unspecified organism matches</t>
+          <t>Rank 1: J18.9 Pneumonia, unspecified organism matches</t>
         </is>
       </c>
       <c r="D63" s="195" t="inlineStr">
@@ -11109,7 +11167,7 @@
       </c>
       <c r="C64" s="193" t="inlineStr">
         <is>
-          <t>Rank 2 — O14.1 Severe pre-eclampsia matches</t>
+          <t>Rank 2: O14.1 Severe pre-eclampsia matches</t>
         </is>
       </c>
       <c r="D64" s="195" t="inlineStr">
@@ -11159,7 +11217,7 @@
       </c>
       <c r="C65" s="193" t="inlineStr">
         <is>
-          <t>Rank 3 — I10 Essential (primary) hypertension matches</t>
+          <t>Rank 3: I10 Essential (primary) hypertension matches</t>
         </is>
       </c>
       <c r="D65" s="195" t="inlineStr">
@@ -11209,7 +11267,7 @@
       </c>
       <c r="C66" s="193" t="inlineStr">
         <is>
-          <t>Rank 4 — A09 Infectious gastroenteritis and colitis matches</t>
+          <t>Rank 4: A09 Infectious gastroenteritis and colitis matches</t>
         </is>
       </c>
       <c r="D66" s="195" t="inlineStr">
@@ -11264,15 +11322,15 @@
       </c>
       <c r="D67" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assign each referral to a period by the date/time referred (ServiceRequest.authoredOn) in Philippine Standard Time, as defined in IND-01.
-Purpose: Monthly reports must not move referrals between months.
+          <t xml:space="preserve">Assign each referral to a period by the date/time referred (ServiceRequest.authoredOn) in Philippine Standard Time. IND-01 defines this rule.
+Purpose: Monthly reports MUST NOT move referrals between months.
 </t>
         </is>
       </c>
       <c r="E67" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Retrieve the Section C referrals C1–C6 that the DOH pre-loaded on the SHR with fixed timestamps (Test Data Section C). Filter the linelist / counts by the Section C reporting month and by the following month. Compare with the Section C Expected Results. Calculation rule: IND-01 (Reference Guide, Ch. 6).
-Mark each sub-item (↳) below; Achieved is counted automatically.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -11497,7 +11555,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" ht="112" customHeight="1" s="125">
+    <row r="71" ht="98.5" customHeight="1" s="125">
       <c r="A71" s="172" t="inlineStr">
         <is>
           <t>L3-18</t>
@@ -11515,15 +11573,15 @@
       </c>
       <c r="D71" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count each referral once by its identifier (IND-02) and exclude cancelled referrals from the active totals while showing them as cancelled (IND-03).
-Purpose: The same referral sent twice, or one that was cancelled, must not inflate the figures.
+          <t xml:space="preserve">Count each referral once by its identifier (IND-02). Exclude cancelled referrals from the active totals, but show them as cancelled (IND-03).
+Purpose: The same referral sent twice, or one that was cancelled, MUST NOT inflate the figures.
 </t>
         </is>
       </c>
       <c r="E71" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3 is a second copy of C2 with the same business identifier and C4 was cancelled by the referring side (both pre-loaded by the DOH). Compare the Section C totals with the Expected Results.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">C3 is a second copy of C2 with the same business identifier. The referring side cancelled C4. The DOH pre-loaded both C3 and C4. Compare the Section C totals with the Expected Results.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -11661,7 +11719,7 @@
       </c>
       <c r="C73" s="193" t="inlineStr">
         <is>
-          <t>Cancelled C4 excluded from active totals and shown as cancelled (IND-03; N/A if cancellation is not supported by the IG version)</t>
+          <t>Cancelled C4 excluded from active totals and shown as cancelled (IND-03, N/A if the IG version does not support cancellation)</t>
         </is>
       </c>
       <c r="D73" s="195" t="inlineStr">
@@ -11698,7 +11756,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="98.5" customHeight="1" s="125">
+    <row r="74" ht="112" customHeight="1" s="125">
       <c r="A74" s="172" t="inlineStr">
         <is>
           <t>L3-19</t>
@@ -11717,14 +11775,16 @@
       <c r="D74" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Report the status as of the time the report is run (IND-04). Compute TAT from the first 'received' timestamp, not from later updates (IND-08).
-Purpose: Reports must follow reality as referrals progress, not freeze at first status.
+Purpose: Reports MUST follow reality as referrals progress, not freeze at the first status.
 </t>
         </is>
       </c>
       <c r="E74" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Run the report. 2. Change C5 from accepted to completed and C2 from received to rejected. 3. Re-run and compare with the Expected Results (after-update column).
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">1. Run the report.
+2. Change C5 from accepted to completed. Change C2 from received to rejected.
+3. Run the report again. Compare the result with the Expected Results (after-update column).
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -11949,7 +12009,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="85" customHeight="1" s="125">
+    <row r="78" ht="98.5" customHeight="1" s="125">
       <c r="A78" s="172" t="inlineStr">
         <is>
           <t>L3-20</t>
@@ -11968,14 +12028,14 @@
       <c r="D78" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Apply report filters together (AND logic) on the same data as the totals.
-Purpose: Managers combine filters; each combination must be correct.
+Purpose: Managers combine filters. Each combination MUST be correct.
 </t>
         </is>
       </c>
       <c r="E78" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply each filter combination listed under the Section C Expected Results (combinations use Section B and Section C data as labelled) and compare.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Apply each filter combination listed under the Section C Expected Results. Combinations use Section B and Section C data as labelled. Compare the results with the Expected Results.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -12219,13 +12279,13 @@
       <c r="D82" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Generate exports from the same query as the screen (IND-09).
-Purpose: Data submitted outside the system must match what users saw.
+Purpose: Data submitted outside the system MUST match what users saw.
 </t>
         </is>
       </c>
       <c r="E82" s="172" t="inlineStr">
         <is>
-          <t>Export the linelist and the aggregate report for the Section B and Section C windows; sum the exported rows. Met only if every total equals the screen and the expected values. Calculation rule: IND-09.</t>
+          <t>Export the linelist and the aggregate report for the Section B and Section C windows. Calculate the sum of the exported rows. Met only if every total equals the screen and the expected values. Calculation rule: IND-09.</t>
         </is>
       </c>
       <c r="F82" s="172" t="inlineStr">
@@ -12350,7 +12410,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12399,7 +12459,7 @@
     <row r="2" ht="79.5" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>Advanced interoperability. Rev 7 separates two tracks: CORE-TRACK items are fundamental interoperability requirements that will MIGRATE to Level 2 (minimum conformance) as soon as the PHeReF IG models them (back-referral and the multi-tier referral chain are not yet modelled in IG v0.1.0); MATURITY items are capability targets that remain optional. Moved to Level 2 in Rev 7: status timestamps (L4-06 → TS2-13), patient de-duplication (L4-08 → TS1-16) and NHFR-sourced facility data (L4-09 → TS0-06.2). The track is shown in the Section column.</t>
+          <t>Advanced interoperability. Rev 7 separates two tracks. Core-track items are fundamental interoperability requirements. They will migrate to Level 2 (minimum conformance) as soon as the PHeReF IG models them. (IG v0.1.0 does not yet model back-referral and the multi-tier referral chain.) Maturity items are capability targets that stay OPTIONAL. Moved to Level 2 in Rev 7: status timestamps (L4-06 → TS2-13), patient de-duplication (L4-08 → TS1-16) and NHFR-sourced facility data (L4-09 → TS0-06.2). The Section column shows the track.</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12485,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -12625,14 +12685,14 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implement back-referral per the PHeReF IG, sent to the SHR and addressed to the original referring facility.
-Purpose: Closes the care loop — the patient's home facility knows what happened.
+          <t xml:space="preserve">Implement back-referral as the PHeReF IG specifies. Send it to the SHR and address it to the original referring facility.
+Purpose: This closes the care loop: the patient's home facility knows what happened.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t>Complete the Test Data referral and send a back-referral; Met if it appears at the referring EMR and on the SHR.</t>
+          <t>Complete the Test Data referral and send a back-referral. Met if it appears at the referring EMR and on the SHR.</t>
         </is>
       </c>
       <c r="F10" s="172" t="inlineStr">
@@ -12716,15 +12776,15 @@
       </c>
       <c r="D11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Include final diagnosis/outcome, treatment given, and follow-up instructions in the back-referral.
+          <t xml:space="preserve">Include final diagnosis/outcome, treatment given and follow-up instructions in the back-referral.
 Purpose: The home facility has what it needs to continue care.
 </t>
         </is>
       </c>
       <c r="E11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the 3 elements present and correct at the referring EMR.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the 3 elements that are present and correct at the referring EMR.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -12949,7 +13009,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="98.5" customHeight="1" s="125">
+    <row r="15" ht="125.5" customHeight="1" s="125">
       <c r="A15" s="172" t="inlineStr">
         <is>
           <t>L4-03</t>
@@ -12967,15 +13027,15 @@
       </c>
       <c r="D15" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-fill the referral form from data already in the patient's record (demographics, vitals, diagnosis) instead of re-entry.
-Purpose: Main gap found at the Connectathon: data was re-keyed instead of reused.
+          <t xml:space="preserve">Pre-fill the referral form from data that is already in the patient's record (demographics, vitals, diagnosis), so that the user does not enter it again.
+Purpose: This was the main gap found at the Connectathon: users re-keyed data instead of reusing it.
 </t>
         </is>
       </c>
       <c r="E15" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Register the test patient with demographics, vitals and diagnosis first. Open a new referral and count the 10 fields listed in the Notes that are pre-filled correctly.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Register the test patient with demographics, vitals and diagnosis first. Open a new referral. Count the 10 fields listed in the Notes that are pre-filled correctly.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -13063,7 +13123,7 @@
       </c>
       <c r="C16" s="193" t="inlineStr">
         <is>
-          <t>Patient full name — pre-filled from the EMR record</t>
+          <t>Patient full name: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D16" s="195" t="inlineStr">
@@ -13113,7 +13173,7 @@
       </c>
       <c r="C17" s="193" t="inlineStr">
         <is>
-          <t>Birth date — pre-filled from the EMR record</t>
+          <t>Birth date: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D17" s="195" t="inlineStr">
@@ -13163,7 +13223,7 @@
       </c>
       <c r="C18" s="193" t="inlineStr">
         <is>
-          <t>Sex — pre-filled from the EMR record</t>
+          <t>Sex: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D18" s="195" t="inlineStr">
@@ -13213,7 +13273,7 @@
       </c>
       <c r="C19" s="193" t="inlineStr">
         <is>
-          <t>PhilSys number — pre-filled from the EMR record</t>
+          <t>PhilSys number: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D19" s="195" t="inlineStr">
@@ -13263,7 +13323,7 @@
       </c>
       <c r="C20" s="193" t="inlineStr">
         <is>
-          <t>PhilHealth ID — pre-filled from the EMR record</t>
+          <t>PhilHealth ID: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D20" s="195" t="inlineStr">
@@ -13313,7 +13373,7 @@
       </c>
       <c r="C21" s="193" t="inlineStr">
         <is>
-          <t>Patient address — pre-filled from the EMR record</t>
+          <t>Patient address: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D21" s="195" t="inlineStr">
@@ -13363,7 +13423,7 @@
       </c>
       <c r="C22" s="193" t="inlineStr">
         <is>
-          <t>Contact number — pre-filled from the EMR record</t>
+          <t>Contact number: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D22" s="195" t="inlineStr">
@@ -13413,7 +13473,7 @@
       </c>
       <c r="C23" s="193" t="inlineStr">
         <is>
-          <t>Chief complaint — pre-filled from the EMR record</t>
+          <t>Chief complaint: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D23" s="195" t="inlineStr">
@@ -13463,7 +13523,7 @@
       </c>
       <c r="C24" s="193" t="inlineStr">
         <is>
-          <t>Working impression — pre-filled from the EMR record</t>
+          <t>Working impression: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D24" s="195" t="inlineStr">
@@ -13513,7 +13573,7 @@
       </c>
       <c r="C25" s="193" t="inlineStr">
         <is>
-          <t>Blood pressure — pre-filled from the EMR record</t>
+          <t>Blood pressure: pre-filled from the EMR record</t>
         </is>
       </c>
       <c r="D25" s="195" t="inlineStr">
@@ -13568,15 +13628,15 @@
       </c>
       <c r="D26" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allow the receiving facility to import the retrieved referral data into its patient record without re-typing.
+          <t xml:space="preserve">Let the receiving facility import the retrieved referral data into its patient record without re-typing.
 Purpose: True interoperability at the receiving side.
 </t>
         </is>
       </c>
       <c r="E26" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the same 10 fields that are imported into the receiving patient record automatically.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the same 10 fields that are imported automatically into the receiving patient record.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -13664,7 +13724,7 @@
       </c>
       <c r="C27" s="193" t="inlineStr">
         <is>
-          <t>Patient full name — imported without re-typing</t>
+          <t>Patient full name: imported without re-typing</t>
         </is>
       </c>
       <c r="D27" s="195" t="inlineStr">
@@ -13714,7 +13774,7 @@
       </c>
       <c r="C28" s="193" t="inlineStr">
         <is>
-          <t>Birth date — imported without re-typing</t>
+          <t>Birth date: imported without re-typing</t>
         </is>
       </c>
       <c r="D28" s="195" t="inlineStr">
@@ -13764,7 +13824,7 @@
       </c>
       <c r="C29" s="193" t="inlineStr">
         <is>
-          <t>Sex — imported without re-typing</t>
+          <t>Sex: imported without re-typing</t>
         </is>
       </c>
       <c r="D29" s="195" t="inlineStr">
@@ -13814,7 +13874,7 @@
       </c>
       <c r="C30" s="193" t="inlineStr">
         <is>
-          <t>PhilSys number — imported without re-typing</t>
+          <t>PhilSys number: imported without re-typing</t>
         </is>
       </c>
       <c r="D30" s="195" t="inlineStr">
@@ -13864,7 +13924,7 @@
       </c>
       <c r="C31" s="193" t="inlineStr">
         <is>
-          <t>PhilHealth ID — imported without re-typing</t>
+          <t>PhilHealth ID: imported without re-typing</t>
         </is>
       </c>
       <c r="D31" s="195" t="inlineStr">
@@ -13914,7 +13974,7 @@
       </c>
       <c r="C32" s="193" t="inlineStr">
         <is>
-          <t>Patient address — imported without re-typing</t>
+          <t>Patient address: imported without re-typing</t>
         </is>
       </c>
       <c r="D32" s="195" t="inlineStr">
@@ -13964,7 +14024,7 @@
       </c>
       <c r="C33" s="193" t="inlineStr">
         <is>
-          <t>Contact number — imported without re-typing</t>
+          <t>Contact number: imported without re-typing</t>
         </is>
       </c>
       <c r="D33" s="195" t="inlineStr">
@@ -14014,7 +14074,7 @@
       </c>
       <c r="C34" s="193" t="inlineStr">
         <is>
-          <t>Chief complaint — imported without re-typing</t>
+          <t>Chief complaint: imported without re-typing</t>
         </is>
       </c>
       <c r="D34" s="195" t="inlineStr">
@@ -14064,7 +14124,7 @@
       </c>
       <c r="C35" s="193" t="inlineStr">
         <is>
-          <t>Working impression — imported without re-typing</t>
+          <t>Working impression: imported without re-typing</t>
         </is>
       </c>
       <c r="D35" s="195" t="inlineStr">
@@ -14114,7 +14174,7 @@
       </c>
       <c r="C36" s="193" t="inlineStr">
         <is>
-          <t>Blood pressure — imported without re-typing</t>
+          <t>Blood pressure: imported without re-typing</t>
         </is>
       </c>
       <c r="D36" s="195" t="inlineStr">
@@ -14164,19 +14224,19 @@
       </c>
       <c r="C37" s="172" t="inlineStr">
         <is>
-          <t>Attachments (e.g., laboratory result PDF) sent with the referral can be opened at the receiving facility (Connectathon Issue #23)</t>
+          <t>Attachments (for example, laboratory result PDF) sent with the referral can be opened at the receiving facility (Connectathon Issue #23)</t>
         </is>
       </c>
       <c r="D37" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store and retrieve attachments (e.g., laboratory result PDF) so they open at the receiving facility.
+          <t xml:space="preserve">Store and retrieve attachments (for example, laboratory result PDF) so that they open at the receiving facility.
 Purpose: Lab results travel with the patient.
 </t>
         </is>
       </c>
       <c r="E37" s="172" t="inlineStr">
         <is>
-          <t>Attach the Test Data lab file (TS1-09); Met if it opens correctly at the receiving EMR.</t>
+          <t>Attach the Test Data lab file (TS1-09). Met if it opens correctly at the receiving EMR.</t>
         </is>
       </c>
       <c r="F37" s="172" t="inlineStr">
@@ -14260,14 +14320,14 @@
       </c>
       <c r="D38" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link each onward referral to the previous one as defined in the IG.
+          <t xml:space="preserve">Link each onward referral to the previous one as the IG defines.
 Purpose: Supports real escalation of care.
 </t>
         </is>
       </c>
       <c r="E38" s="172" t="inlineStr">
         <is>
-          <t>Perform a 3-step referral chain; Met if the SHR shows each referral linked to the previous one.</t>
+          <t>Do a 3-step referral chain. Met if the SHR shows each referral linked to the previous one.</t>
         </is>
       </c>
       <c r="F38" s="172" t="inlineStr">
@@ -14351,14 +14411,14 @@
       </c>
       <c r="D39" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support cancel / revoke of a referral and send the status to the receiving facility (if supported by the IG version).
-Purpose: Prevents facilities preparing for patients who are not coming.
+          <t xml:space="preserve">Support cancel / revoke of a referral, and send the status to the receiving facility (if the IG version supports it).
+Purpose: This prevents facilities from preparing for patients who are not coming.
 </t>
         </is>
       </c>
       <c r="E39" s="172" t="inlineStr">
         <is>
-          <t>Cancel one test referral; Met if the receiving EMR shows it as cancelled. Mark N/A with reason if not yet supported by the IG version tested.</t>
+          <t>Cancel one test referral. Met if the receiving EMR shows it as cancelled. If the tested IG version does not support it yet, mark N/A with the reason.</t>
         </is>
       </c>
       <c r="F39" s="172" t="inlineStr">
@@ -14483,7 +14543,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -16743,7 +16803,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" ht="64" customHeight="1" s="125">
+    <row r="136" ht="88" customHeight="1" s="125">
       <c r="A136" s="242" t="n"/>
       <c r="B136" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L0 Application'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L0 Application'!D10)-1),'L0 Application'!D10)</f>
@@ -16783,7 +16843,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" ht="64" customHeight="1" s="125">
+    <row r="138" ht="76" customHeight="1" s="125">
       <c r="A138" s="242" t="n"/>
       <c r="B138" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L0 Application'!D11,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L0 Application'!D11)-1),'L0 Application'!D11)</f>
@@ -16963,7 +17023,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" ht="64" customHeight="1" s="125">
+    <row r="147" ht="76" customHeight="1" s="125">
       <c r="A147" s="242" t="n"/>
       <c r="B147" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L0 Application'!D17,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L0 Application'!D17)-1),'L0 Application'!D17)</f>
@@ -17386,7 +17446,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" ht="304" customHeight="1" s="125">
+    <row r="169" ht="328" customHeight="1" s="125">
       <c r="A169" s="242" t="n"/>
       <c r="B169" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L1 Documentation'!D20,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L1 Documentation'!D20)-1),'L1 Documentation'!D20)</f>
@@ -17426,7 +17486,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" ht="304" customHeight="1" s="125">
+    <row r="171" ht="340" customHeight="1" s="125">
       <c r="A171" s="242" t="n"/>
       <c r="B171" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L1 Documentation'!D21,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L1 Documentation'!D21)-1),'L1 Documentation'!D21)</f>
@@ -17566,7 +17626,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" ht="40" customHeight="1" s="125">
+    <row r="178" ht="64" customHeight="1" s="125">
       <c r="A178" s="242" t="n"/>
       <c r="B178" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L1 Documentation'!D27,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L1 Documentation'!D27)-1),'L1 Documentation'!D27)</f>
@@ -17749,7 +17809,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" ht="220" customHeight="1" s="125">
+    <row r="188" ht="280" customHeight="1" s="125">
       <c r="A188" s="242" t="n"/>
       <c r="B188" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-A TS0-Terminology'!D15,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-A TS0-Terminology'!D15)-1),'L2-A TS0-Terminology'!D15)</f>
@@ -17889,7 +17949,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" ht="124" customHeight="1" s="125">
+    <row r="195" ht="136" customHeight="1" s="125">
       <c r="A195" s="242" t="n"/>
       <c r="B195" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-A TS0-Terminology'!D21,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-A TS0-Terminology'!D21)-1),'L2-A TS0-Terminology'!D21)</f>
@@ -17929,7 +17989,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" ht="88" customHeight="1" s="125">
+    <row r="197" ht="100" customHeight="1" s="125">
       <c r="A197" s="242" t="n"/>
       <c r="B197" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-A TS0-Terminology'!D22,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-A TS0-Terminology'!D22)-1),'L2-A TS0-Terminology'!D22)</f>
@@ -18229,7 +18289,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" ht="208" customHeight="1" s="125">
+    <row r="212" ht="232" customHeight="1" s="125">
       <c r="A212" s="242" t="n"/>
       <c r="B212" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-A TS0-Terminology'!D34,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-A TS0-Terminology'!D34)-1),'L2-A TS0-Terminology'!D34)</f>
@@ -18309,7 +18369,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" ht="112" customHeight="1" s="125">
+    <row r="216" ht="136" customHeight="1" s="125">
       <c r="A216" s="242" t="n"/>
       <c r="B216" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-A TS0-Terminology'!D37,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-A TS0-Terminology'!D37)-1),'L2-A TS0-Terminology'!D37)</f>
@@ -18372,7 +18432,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" ht="184" customHeight="1" s="125">
+    <row r="220" ht="220" customHeight="1" s="125">
       <c r="A220" s="242" t="n"/>
       <c r="B220" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D10)-1),'L2-B TS1-Submission'!D10)</f>
@@ -18512,7 +18572,7 @@
         <v/>
       </c>
     </row>
-    <row r="227" ht="184" customHeight="1" s="125">
+    <row r="227" ht="220" customHeight="1" s="125">
       <c r="A227" s="242" t="n"/>
       <c r="B227" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D16,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D16)-1),'L2-B TS1-Submission'!D16)</f>
@@ -18612,7 +18672,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" ht="208" customHeight="1" s="125">
+    <row r="232" ht="232" customHeight="1" s="125">
       <c r="A232" s="242" t="n"/>
       <c r="B232" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D20,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D20)-1),'L2-B TS1-Submission'!D20)</f>
@@ -18732,7 +18792,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" ht="232" customHeight="1" s="125">
+    <row r="238" ht="256" customHeight="1" s="125">
       <c r="A238" s="242" t="n"/>
       <c r="B238" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D25,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D25)-1),'L2-B TS1-Submission'!D25)</f>
@@ -18952,7 +19012,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" ht="148" customHeight="1" s="125">
+    <row r="249" ht="196" customHeight="1" s="125">
       <c r="A249" s="242" t="n"/>
       <c r="B249" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D35,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D35)-1),'L2-B TS1-Submission'!D35)</f>
@@ -18992,7 +19052,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" ht="220" customHeight="1" s="125">
+    <row r="251" ht="244" customHeight="1" s="125">
       <c r="A251" s="242" t="n"/>
       <c r="B251" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D36,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D36)-1),'L2-B TS1-Submission'!D36)</f>
@@ -19106,7 +19166,7 @@
         <v/>
       </c>
     </row>
-    <row r="257" ht="16" customHeight="1" s="125">
+    <row r="257" ht="29" customHeight="1" s="125">
       <c r="A257" s="244">
         <f>'L2-B TS1-Submission'!A42</f>
         <v/>
@@ -19152,7 +19212,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" ht="208" customHeight="1" s="125">
+    <row r="259" ht="220" customHeight="1" s="125">
       <c r="A259" s="242" t="n"/>
       <c r="B259" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D43,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D43)-1),'L2-B TS1-Submission'!D43)</f>
@@ -19252,7 +19312,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" ht="196" customHeight="1" s="125">
+    <row r="264" ht="220" customHeight="1" s="125">
       <c r="A264" s="242" t="n"/>
       <c r="B264" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D47,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D47)-1),'L2-B TS1-Submission'!D47)</f>
@@ -19412,7 +19472,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" ht="124" customHeight="1" s="125">
+    <row r="272" ht="148" customHeight="1" s="125">
       <c r="A272" s="242" t="n"/>
       <c r="B272" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D54,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D54)-1),'L2-B TS1-Submission'!D54)</f>
@@ -19452,7 +19512,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" ht="124" customHeight="1" s="125">
+    <row r="274" ht="148" customHeight="1" s="125">
       <c r="A274" s="242" t="n"/>
       <c r="B274" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D55,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D55)-1),'L2-B TS1-Submission'!D55)</f>
@@ -19492,7 +19552,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" ht="184" customHeight="1" s="125">
+    <row r="276" ht="220" customHeight="1" s="125">
       <c r="A276" s="242" t="n"/>
       <c r="B276" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D56,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D56)-1),'L2-B TS1-Submission'!D56)</f>
@@ -19572,7 +19632,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" ht="196" customHeight="1" s="125">
+    <row r="280" ht="220" customHeight="1" s="125">
       <c r="A280" s="242" t="n"/>
       <c r="B280" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D59,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D59)-1),'L2-B TS1-Submission'!D59)</f>
@@ -19692,7 +19752,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" ht="112" customHeight="1" s="125">
+    <row r="286" ht="136" customHeight="1" s="125">
       <c r="A286" s="242" t="n"/>
       <c r="B286" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D64,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D64)-1),'L2-B TS1-Submission'!D64)</f>
@@ -19732,7 +19792,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" ht="40" customHeight="1" s="125">
+    <row r="288" ht="52" customHeight="1" s="125">
       <c r="A288" s="242" t="n"/>
       <c r="B288" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D65,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D65)-1),'L2-B TS1-Submission'!D65)</f>
@@ -19812,7 +19872,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" ht="160" customHeight="1" s="125">
+    <row r="292" ht="184" customHeight="1" s="125">
       <c r="A292" s="242" t="n"/>
       <c r="B292" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D67,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D67)-1),'L2-B TS1-Submission'!D67)</f>
@@ -19912,7 +19972,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" ht="124" customHeight="1" s="125">
+    <row r="297" ht="148" customHeight="1" s="125">
       <c r="A297" s="242" t="n"/>
       <c r="B297" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D71,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D71)-1),'L2-B TS1-Submission'!D71)</f>
@@ -20292,7 +20352,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" ht="124" customHeight="1" s="125">
+    <row r="316" ht="160" customHeight="1" s="125">
       <c r="A316" s="242" t="n"/>
       <c r="B316" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-B TS1-Submission'!D87,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-B TS1-Submission'!D87)-1),'L2-B TS1-Submission'!D87)</f>
@@ -20355,7 +20415,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" ht="100" customHeight="1" s="125">
+    <row r="320" ht="124" customHeight="1" s="125">
       <c r="A320" s="242" t="n"/>
       <c r="B320" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D10)-1),'L2-C TS2-Retrieval'!D10)</f>
@@ -20395,7 +20455,7 @@
         <v/>
       </c>
     </row>
-    <row r="322" ht="196" customHeight="1" s="125">
+    <row r="322" ht="220" customHeight="1" s="125">
       <c r="A322" s="242" t="n"/>
       <c r="B322" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D11,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D11)-1),'L2-C TS2-Retrieval'!D11)</f>
@@ -20549,7 +20609,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" ht="56" customHeight="1" s="125">
+    <row r="330" ht="43" customHeight="1" s="125">
       <c r="A330" s="238">
         <f>'L2-C TS2-Retrieval'!A19</f>
         <v/>
@@ -20575,7 +20635,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" ht="196" customHeight="1" s="125">
+    <row r="331" ht="220" customHeight="1" s="125">
       <c r="A331" s="242" t="n"/>
       <c r="B331" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D19,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D19)-1),'L2-C TS2-Retrieval'!D19)</f>
@@ -20675,7 +20735,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" ht="196" customHeight="1" s="125">
+    <row r="336" ht="220" customHeight="1" s="125">
       <c r="A336" s="242" t="n"/>
       <c r="B336" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D23,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D23)-1),'L2-C TS2-Retrieval'!D23)</f>
@@ -20935,7 +20995,7 @@
         <v/>
       </c>
     </row>
-    <row r="349" ht="196" customHeight="1" s="125">
+    <row r="349" ht="220" customHeight="1" s="125">
       <c r="A349" s="242" t="n"/>
       <c r="B349" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D35,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D35)-1),'L2-C TS2-Retrieval'!D35)</f>
@@ -21055,7 +21115,7 @@
         <v/>
       </c>
     </row>
-    <row r="355" ht="196" customHeight="1" s="125">
+    <row r="355" ht="220" customHeight="1" s="125">
       <c r="A355" s="242" t="n"/>
       <c r="B355" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D40,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D40)-1),'L2-C TS2-Retrieval'!D40)</f>
@@ -21175,7 +21235,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" ht="196" customHeight="1" s="125">
+    <row r="361" ht="220" customHeight="1" s="125">
       <c r="A361" s="242" t="n"/>
       <c r="B361" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D45,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D45)-1),'L2-C TS2-Retrieval'!D45)</f>
@@ -21335,7 +21395,7 @@
         <v/>
       </c>
     </row>
-    <row r="369" ht="100" customHeight="1" s="125">
+    <row r="369" ht="124" customHeight="1" s="125">
       <c r="A369" s="242" t="n"/>
       <c r="B369" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D52,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D52)-1),'L2-C TS2-Retrieval'!D52)</f>
@@ -21375,7 +21435,7 @@
         <v/>
       </c>
     </row>
-    <row r="371" ht="196" customHeight="1" s="125">
+    <row r="371" ht="220" customHeight="1" s="125">
       <c r="A371" s="242" t="n"/>
       <c r="B371" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D53,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D53)-1),'L2-C TS2-Retrieval'!D53)</f>
@@ -21475,7 +21535,7 @@
         <v/>
       </c>
     </row>
-    <row r="376" ht="232" customHeight="1" s="125">
+    <row r="376" ht="268" customHeight="1" s="125">
       <c r="A376" s="242" t="n"/>
       <c r="B376" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D57,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D57)-1),'L2-C TS2-Retrieval'!D57)</f>
@@ -21549,7 +21609,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" ht="42" customHeight="1" s="125">
+    <row r="380" ht="29" customHeight="1" s="125">
       <c r="A380" s="244">
         <f>'L2-C TS2-Retrieval'!A61</f>
         <v/>
@@ -21595,7 +21655,7 @@
         <v/>
       </c>
     </row>
-    <row r="382" ht="172" customHeight="1" s="125">
+    <row r="382" ht="196" customHeight="1" s="125">
       <c r="A382" s="242" t="n"/>
       <c r="B382" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D62,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D62)-1),'L2-C TS2-Retrieval'!D62)</f>
@@ -21715,7 +21775,7 @@
         <v/>
       </c>
     </row>
-    <row r="388" ht="112" customHeight="1" s="125">
+    <row r="388" ht="136" customHeight="1" s="125">
       <c r="A388" s="242" t="n"/>
       <c r="B388" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D67,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D67)-1),'L2-C TS2-Retrieval'!D67)</f>
@@ -21755,7 +21815,7 @@
         <v/>
       </c>
     </row>
-    <row r="390" ht="160" customHeight="1" s="125">
+    <row r="390" ht="184" customHeight="1" s="125">
       <c r="A390" s="242" t="n"/>
       <c r="B390" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-C TS2-Retrieval'!D68,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-C TS2-Retrieval'!D68)-1),'L2-C TS2-Retrieval'!D68)</f>
@@ -21898,7 +21958,7 @@
         <v/>
       </c>
     </row>
-    <row r="398" ht="112" customHeight="1" s="125">
+    <row r="398" ht="148" customHeight="1" s="125">
       <c r="A398" s="242" t="n"/>
       <c r="B398" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D10)-1),'L2-D System Resilience'!D10)</f>
@@ -21938,7 +21998,7 @@
         <v/>
       </c>
     </row>
-    <row r="400" ht="88" customHeight="1" s="125">
+    <row r="400" ht="100" customHeight="1" s="125">
       <c r="A400" s="242" t="n"/>
       <c r="B400" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D11,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D11)-1),'L2-D System Resilience'!D11)</f>
@@ -21978,7 +22038,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" ht="64" customHeight="1" s="125">
+    <row r="402" ht="88" customHeight="1" s="125">
       <c r="A402" s="242" t="n"/>
       <c r="B402" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D12,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D12)-1),'L2-D System Resilience'!D12)</f>
@@ -22378,7 +22438,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" ht="268" customHeight="1" s="125">
+    <row r="422" ht="304" customHeight="1" s="125">
       <c r="A422" s="242" t="n"/>
       <c r="B422" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D29,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D29)-1),'L2-D System Resilience'!D29)</f>
@@ -22418,7 +22478,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" ht="292" customHeight="1" s="125">
+    <row r="424" ht="328" customHeight="1" s="125">
       <c r="A424" s="242" t="n"/>
       <c r="B424" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D30,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D30)-1),'L2-D System Resilience'!D30)</f>
@@ -22598,7 +22658,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" ht="124" customHeight="1" s="125">
+    <row r="433" ht="148" customHeight="1" s="125">
       <c r="A433" s="242" t="n"/>
       <c r="B433" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D37,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D37)-1),'L2-D System Resilience'!D37)</f>
@@ -22672,7 +22732,7 @@
         <v/>
       </c>
     </row>
-    <row r="437" ht="56" customHeight="1" s="125">
+    <row r="437" ht="69" customHeight="1" s="125">
       <c r="A437" s="238">
         <f>'L2-D System Resilience'!A41</f>
         <v/>
@@ -22698,7 +22758,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" ht="124" customHeight="1" s="125">
+    <row r="438" ht="136" customHeight="1" s="125">
       <c r="A438" s="242" t="n"/>
       <c r="B438" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D41,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D41)-1),'L2-D System Resilience'!D41)</f>
@@ -22798,7 +22858,7 @@
         <v/>
       </c>
     </row>
-    <row r="443" ht="100" customHeight="1" s="125">
+    <row r="443" ht="112" customHeight="1" s="125">
       <c r="A443" s="242" t="n"/>
       <c r="B443" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D45,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D45)-1),'L2-D System Resilience'!D45)</f>
@@ -22918,7 +22978,7 @@
         <v/>
       </c>
     </row>
-    <row r="449" ht="136" customHeight="1" s="125">
+    <row r="449" ht="148" customHeight="1" s="125">
       <c r="A449" s="242" t="n"/>
       <c r="B449" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D50,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D50)-1),'L2-D System Resilience'!D50)</f>
@@ -22998,7 +23058,7 @@
         <v/>
       </c>
     </row>
-    <row r="453" ht="124" customHeight="1" s="125">
+    <row r="453" ht="148" customHeight="1" s="125">
       <c r="A453" s="242" t="n"/>
       <c r="B453" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D53,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D53)-1),'L2-D System Resilience'!D53)</f>
@@ -23038,7 +23098,7 @@
         <v/>
       </c>
     </row>
-    <row r="455" ht="220" customHeight="1" s="125">
+    <row r="455" ht="256" customHeight="1" s="125">
       <c r="A455" s="242" t="n"/>
       <c r="B455" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D54,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D54)-1),'L2-D System Resilience'!D54)</f>
@@ -23138,7 +23198,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" ht="160" customHeight="1" s="125">
+    <row r="460" ht="220" customHeight="1" s="125">
       <c r="A460" s="242" t="n"/>
       <c r="B460" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D58,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D58)-1),'L2-D System Resilience'!D58)</f>
@@ -23238,7 +23298,7 @@
         <v/>
       </c>
     </row>
-    <row r="465" ht="136" customHeight="1" s="125">
+    <row r="465" ht="172" customHeight="1" s="125">
       <c r="A465" s="242" t="n"/>
       <c r="B465" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D62,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D62)-1),'L2-D System Resilience'!D62)</f>
@@ -23318,7 +23378,7 @@
         <v/>
       </c>
     </row>
-    <row r="469" ht="208" customHeight="1" s="125">
+    <row r="469" ht="232" customHeight="1" s="125">
       <c r="A469" s="242" t="n"/>
       <c r="B469" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D65,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D65)-1),'L2-D System Resilience'!D65)</f>
@@ -23398,7 +23458,7 @@
         <v/>
       </c>
     </row>
-    <row r="473" ht="208" customHeight="1" s="125">
+    <row r="473" ht="232" customHeight="1" s="125">
       <c r="A473" s="242" t="n"/>
       <c r="B473" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D68,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D68)-1),'L2-D System Resilience'!D68)</f>
@@ -23498,7 +23558,7 @@
         <v/>
       </c>
     </row>
-    <row r="478" ht="196" customHeight="1" s="125">
+    <row r="478" ht="220" customHeight="1" s="125">
       <c r="A478" s="242" t="n"/>
       <c r="B478" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D72,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D72)-1),'L2-D System Resilience'!D72)</f>
@@ -23578,7 +23638,7 @@
         <v/>
       </c>
     </row>
-    <row r="482" ht="172" customHeight="1" s="125">
+    <row r="482" ht="220" customHeight="1" s="125">
       <c r="A482" s="242" t="n"/>
       <c r="B482" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D75,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D75)-1),'L2-D System Resilience'!D75)</f>
@@ -23658,7 +23718,7 @@
         <v/>
       </c>
     </row>
-    <row r="486" ht="160" customHeight="1" s="125">
+    <row r="486" ht="208" customHeight="1" s="125">
       <c r="A486" s="242" t="n"/>
       <c r="B486" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D78,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D78)-1),'L2-D System Resilience'!D78)</f>
@@ -23698,7 +23758,7 @@
         <v/>
       </c>
     </row>
-    <row r="488" ht="160" customHeight="1" s="125">
+    <row r="488" ht="196" customHeight="1" s="125">
       <c r="A488" s="242" t="n"/>
       <c r="B488" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L2-D System Resilience'!D79,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L2-D System Resilience'!D79)-1),'L2-D System Resilience'!D79)</f>
@@ -23821,7 +23881,7 @@
         <v/>
       </c>
     </row>
-    <row r="495" ht="88" customHeight="1" s="125">
+    <row r="495" ht="100" customHeight="1" s="125">
       <c r="A495" s="242" t="n"/>
       <c r="B495" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D10)-1),'L3 Reports'!D10)</f>
@@ -23981,7 +24041,7 @@
         <v/>
       </c>
     </row>
-    <row r="503" ht="52" customHeight="1" s="125">
+    <row r="503" ht="76" customHeight="1" s="125">
       <c r="A503" s="242" t="n"/>
       <c r="B503" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D17,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D17)-1),'L3 Reports'!D17)</f>
@@ -24141,7 +24201,7 @@
         <v/>
       </c>
     </row>
-    <row r="511" ht="64" customHeight="1" s="125">
+    <row r="511" ht="76" customHeight="1" s="125">
       <c r="A511" s="242" t="n"/>
       <c r="B511" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D24,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D24)-1),'L3 Reports'!D24)</f>
@@ -24181,7 +24241,7 @@
         <v/>
       </c>
     </row>
-    <row r="513" ht="76" customHeight="1" s="125">
+    <row r="513" ht="88" customHeight="1" s="125">
       <c r="A513" s="242" t="n"/>
       <c r="B513" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D25,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D25)-1),'L3 Reports'!D25)</f>
@@ -24281,7 +24341,7 @@
         <v/>
       </c>
     </row>
-    <row r="518" ht="76" customHeight="1" s="125">
+    <row r="518" ht="88" customHeight="1" s="125">
       <c r="A518" s="242" t="n"/>
       <c r="B518" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D29,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D29)-1),'L3 Reports'!D29)</f>
@@ -24361,7 +24421,7 @@
         <v/>
       </c>
     </row>
-    <row r="522" ht="76" customHeight="1" s="125">
+    <row r="522" ht="88" customHeight="1" s="125">
       <c r="A522" s="242" t="n"/>
       <c r="B522" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D32,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D32)-1),'L3 Reports'!D32)</f>
@@ -24481,7 +24541,7 @@
         <v/>
       </c>
     </row>
-    <row r="528" ht="76" customHeight="1" s="125">
+    <row r="528" ht="88" customHeight="1" s="125">
       <c r="A528" s="242" t="n"/>
       <c r="B528" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D37,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D37)-1),'L3 Reports'!D37)</f>
@@ -24601,7 +24661,7 @@
         <v/>
       </c>
     </row>
-    <row r="534" ht="76" customHeight="1" s="125">
+    <row r="534" ht="88" customHeight="1" s="125">
       <c r="A534" s="242" t="n"/>
       <c r="B534" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D42,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D42)-1),'L3 Reports'!D42)</f>
@@ -24901,7 +24961,7 @@
         <v/>
       </c>
     </row>
-    <row r="549" ht="64" customHeight="1" s="125">
+    <row r="549" ht="76" customHeight="1" s="125">
       <c r="A549" s="242" t="n"/>
       <c r="B549" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D52,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D52)-1),'L3 Reports'!D52)</f>
@@ -25041,7 +25101,7 @@
         <v/>
       </c>
     </row>
-    <row r="556" ht="52" customHeight="1" s="125">
+    <row r="556" ht="64" customHeight="1" s="125">
       <c r="A556" s="242" t="n"/>
       <c r="B556" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D57,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D57)-1),'L3 Reports'!D57)</f>
@@ -25161,7 +25221,7 @@
         <v/>
       </c>
     </row>
-    <row r="562" ht="88" customHeight="1" s="125">
+    <row r="562" ht="100" customHeight="1" s="125">
       <c r="A562" s="242" t="n"/>
       <c r="B562" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D62,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D62)-1),'L3 Reports'!D62)</f>
@@ -25281,7 +25341,7 @@
         <v/>
       </c>
     </row>
-    <row r="568" ht="100" customHeight="1" s="125">
+    <row r="568" ht="112" customHeight="1" s="125">
       <c r="A568" s="242" t="n"/>
       <c r="B568" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D67,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D67)-1),'L3 Reports'!D67)</f>
@@ -25381,7 +25441,7 @@
         <v/>
       </c>
     </row>
-    <row r="573" ht="88" customHeight="1" s="125">
+    <row r="573" ht="100" customHeight="1" s="125">
       <c r="A573" s="242" t="n"/>
       <c r="B573" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D71,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D71)-1),'L3 Reports'!D71)</f>
@@ -25461,7 +25521,7 @@
         <v/>
       </c>
     </row>
-    <row r="577" ht="88" customHeight="1" s="125">
+    <row r="577" ht="124" customHeight="1" s="125">
       <c r="A577" s="242" t="n"/>
       <c r="B577" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D74,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D74)-1),'L3 Reports'!D74)</f>
@@ -25561,7 +25621,7 @@
         <v/>
       </c>
     </row>
-    <row r="582" ht="76" customHeight="1" s="125">
+    <row r="582" ht="100" customHeight="1" s="125">
       <c r="A582" s="242" t="n"/>
       <c r="B582" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L3 Reports'!D78,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L3 Reports'!D78)-1),'L3 Reports'!D78)</f>
@@ -25724,7 +25784,7 @@
         <v/>
       </c>
     </row>
-    <row r="591" ht="40" customHeight="1" s="125">
+    <row r="591" ht="52" customHeight="1" s="125">
       <c r="A591" s="242" t="n"/>
       <c r="B591" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L4 Advanced'!D10,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L4 Advanced'!D10)-1),'L4 Advanced'!D10)</f>
@@ -25764,7 +25824,7 @@
         <v/>
       </c>
     </row>
-    <row r="593" ht="64" customHeight="1" s="125">
+    <row r="593" ht="76" customHeight="1" s="125">
       <c r="A593" s="242" t="n"/>
       <c r="B593" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L4 Advanced'!D11,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L4 Advanced'!D11)-1),'L4 Advanced'!D11)</f>
@@ -25864,7 +25924,7 @@
         <v/>
       </c>
     </row>
-    <row r="598" ht="76" customHeight="1" s="125">
+    <row r="598" ht="88" customHeight="1" s="125">
       <c r="A598" s="242" t="n"/>
       <c r="B598" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L4 Advanced'!D15,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L4 Advanced'!D15)-1),'L4 Advanced'!D15)</f>
@@ -26038,7 +26098,7 @@
         <v/>
       </c>
     </row>
-    <row r="607" ht="29" customHeight="1" s="125">
+    <row r="607" ht="16" customHeight="1" s="125">
       <c r="A607" s="244">
         <f>'L4 Advanced'!A24</f>
         <v/>
@@ -26104,7 +26164,7 @@
         <v/>
       </c>
     </row>
-    <row r="610" ht="64" customHeight="1" s="125">
+    <row r="610" ht="76" customHeight="1" s="125">
       <c r="A610" s="242" t="n"/>
       <c r="B610" s="243">
         <f>"Developer's Guide: "&amp;IFERROR(LEFT('L4 Advanced'!D26,FIND(CHAR(10)&amp;CHAR(10)&amp;"Purpose:",'L4 Advanced'!D26)-1),'L4 Advanced'!D26)</f>
@@ -27252,7 +27312,7 @@
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.7" header="0.511811023622047" footer="0.25"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;L&amp;7 Healthcare Interoperability Readiness Matrix for EMR Systems&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -28562,7 +28622,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -29154,7 +29214,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32465,7 +32525,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -32514,7 +32574,7 @@
     <row r="2" ht="48" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>The vendor/developer formally applies and commits to the process. All items are documents. Critical items (red) must all be Met.</t>
+          <t>The vendor/developer formally applies and commits to the process. All items are documents. Critical items (red) MUST all be Met.</t>
         </is>
       </c>
     </row>
@@ -32540,7 +32600,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -32735,19 +32795,22 @@
       </c>
       <c r="C10" s="172" t="inlineStr">
         <is>
-          <t>Letter of application to have the EMR system tested for use in the HIE, signed by the vendor's/developer's authorized signatory</t>
+          <t>Letter of application to have the EMR system tested for use in the HIE, signed by the authorized signatory of the vendor/developer</t>
         </is>
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit a letter of application on official letterhead, signed by an authorized signatory, with proof of authority (secretary's certificate / board resolution; office order for in-house systems).
-Purpose: The vendor or developer formally asks to be evaluated.
+          <t xml:space="preserve">Submit a letter of application on official letterhead, signed by an authorized signatory. Attach proof of authority: a secretary's certificate / board resolution, or an office order for in-house systems.
+Purpose: The vendor or developer formally asks for an evaluation.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t>Check the letter is on official letterhead, dated, and signed by an authorized signatory (with proof of authority, e.g. secretary's certificate or office order for in-house systems).</t>
+          <t xml:space="preserve">Check that the letter is on official letterhead and has a date.
+Check that an authorized signatory signed the letter.
+Check the proof of authority (for example, a secretary's certificate, or an office order for in-house systems).
+</t>
         </is>
       </c>
       <c r="F10" s="172" t="inlineStr">
@@ -32813,7 +32876,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="112" customHeight="1" s="125">
+    <row r="11" ht="125.5" customHeight="1" s="125">
       <c r="A11" s="172" t="inlineStr">
         <is>
           <t>L0-02</t>
@@ -32831,15 +32894,15 @@
       </c>
       <c r="D11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name three contact persons — product/technical lead, FHIR integration developer, data privacy contact — with position, email and mobile number.
+          <t xml:space="preserve">Name three contact persons: the product/technical lead, the FHIR integration developer and the data privacy contact. Give the position, email and mobile number of each person.
 Purpose: The DOH knows who is accountable for the product, the integration and privacy questions during testing.
 </t>
         </is>
       </c>
       <c r="E11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the roles with a named person, position and contact details in the letter or designation.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the roles that have a named person, position and contact details in the letter or designation.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -33082,14 +33145,14 @@
       </c>
       <c r="D15" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complete the System Profile Sheet: product name, exact version/build to be tested, deployment model, and facility types the system is offered for.
-Purpose: We know exactly which system and version is being tested; results apply to that version only.
+          <t xml:space="preserve">Complete the System Profile Sheet: product name, exact version/build for testing, deployment model, and the facility types that the system is offered for.
+Purpose: We know exactly which system and version we test. The results apply to that version only.
 </t>
         </is>
       </c>
       <c r="E15" s="172" t="inlineStr">
         <is>
-          <t>Check System Profile A.1–A.7 and B.1–B.2 are complete and match the letter.</t>
+          <t>Check that System Profile A.1 to A.7 and B.1 to B.2 are complete and agree with the letter.</t>
         </is>
       </c>
       <c r="F15" s="172" t="inlineStr">
@@ -33173,14 +33236,14 @@
       </c>
       <c r="D16" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign the undertaking to (1) conform to PH Core and PHeReF, (2) request re-testing on IG version change or major release, and (3) use only test data on the sandbox.
-Purpose: Because the IGs are drafts, the vendor agrees to keep up with updates; no real patient data is used in testing.
+          <t xml:space="preserve">Sign the undertaking to: (1) conform to PH Core and PHeReF, (2) request re-testing on IG version change or major release, and (3) use only test data on the sandbox.
+Purpose: The IGs are drafts. Thus the vendor agrees to stay current with the IG updates. Testing uses no real patient data.
 </t>
         </is>
       </c>
       <c r="E16" s="172" t="inlineStr">
         <is>
-          <t>Check the signed undertaking names both IGs, the re-test clause and the test-data-only clause.</t>
+          <t>Check that the signed undertaking names both IGs, the re-test clause and the test-data-only clause.</t>
         </is>
       </c>
       <c r="F16" s="172" t="inlineStr">
@@ -33246,7 +33309,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="112" customHeight="1" s="125">
+    <row r="17" ht="125.5" customHeight="1" s="125">
       <c r="A17" s="172" t="inlineStr">
         <is>
           <t>L0-05</t>
@@ -33264,15 +33327,15 @@
       </c>
       <c r="D17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ensure the three contact persons attend the initial coordination meeting with the Regional Validation Team (in person or virtual) to agree on the process and schedule.
+          <t xml:space="preserve">Ensure that the three contact persons attend the initial coordination meeting with the Regional Validation Team (in person or virtual). At the meeting, they agree on the process and the schedule.
 Purpose: The vendor understands the process and the schedule before testing begins.
 </t>
         </is>
       </c>
       <c r="E17" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the contact persons in the attendance / minutes of the coordination meeting.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the contact persons in the attendance sheet / minutes of the coordination meeting.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -33515,7 +33578,7 @@
       </c>
       <c r="D21" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request sandbox (test endpoint) access from the Regional Validation Team and confirm a successful connection.
+          <t xml:space="preserve">Request sandbox (test endpoint) access from the Regional Validation Team. Confirm that the connection is successful.
 Purpose: The vendor can connect to the test servers.
 </t>
         </is>
@@ -33647,7 +33710,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -33722,7 +33785,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -33904,7 +33967,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="112" customHeight="1" s="125">
+    <row r="10" ht="125.5" customHeight="1" s="125">
       <c r="A10" s="172" t="inlineStr">
         <is>
           <t>L1-01</t>
@@ -33917,19 +33980,19 @@
       </c>
       <c r="C10" s="172" t="inlineStr">
         <is>
-          <t>Process flows of the eReferral module as implemented in the system, for ALL three: (a) referring, (b) receiving, (c) back-referral</t>
+          <t>Process flows of the eReferral module as implemented in the system, for all three: (a) referring, (b) receiving, (c) back-referral</t>
         </is>
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit process flow diagrams of the eReferral module for referring, receiving and back-referral, showing the actual system screens and steps.
-Purpose: Shows how the system moves a referral step by step. All three are required (all-or-nothing, per DOH draft).
+          <t xml:space="preserve">Submit process flow diagrams of the eReferral module for referring, receiving and back-referral. Show the actual system screens and steps in the diagrams.
+Purpose: Shows how the system moves a referral step by step. All three diagrams are REQUIRED (all-or-nothing, per DOH draft).
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t>Check that diagrams exist for all three flows and show the system screens/steps. If any one is missing, mark Not Met.</t>
+          <t>Check that diagrams exist for all three flows and show the system screens/steps. If any one diagram is missing, mark Not Met.</t>
         </is>
       </c>
       <c r="F10" s="172" t="inlineStr">
@@ -34008,20 +34071,20 @@
       </c>
       <c r="C11" s="172" t="inlineStr">
         <is>
-          <t>User manual of the eReferral module contains ALL seven required sections (all-or-nothing): (1) system overview &amp; user roles, (2) referring workflow step-by-step, (3) receiving workflow step-by-step, (4) back-referral workflow, (5) downtime/offline behaviour, (6) troubleshooting &amp; error messages, (7) vendor support contacts &amp; escalation</t>
+          <t>User manual of the eReferral module contains all seven REQUIRED sections (all-or-nothing): (1) system overview &amp; user roles, (2) referring workflow step-by-step, (3) receiving workflow step-by-step, (4) back-referral workflow, (5) downtime/offline behaviour, (6) troubleshooting &amp; error messages, (7) vendor support contacts &amp; escalation</t>
         </is>
       </c>
       <c r="D11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit the eReferral module user manual with a table of contents covering ALL 7 required sections, including how users check the server status and what the system does during downtime or offline operation. Titles, order and format (printed, PDF or online help) are the vendor's choice — only the content is checked.
-Purpose: Checks the CONTENT of the manual once, at product level. All seven sections are required: a manual missing any one section scores 0% (all-or-nothing).
+          <t xml:space="preserve">Submit the eReferral module user manual with a table of contents that covers all 7 REQUIRED sections. Include how users check the server status. Include what the system does during downtime or offline operation. The vendor MAY choose the titles, order and format (printed, PDF or online help). The validation checks only the content.
+Purpose: Checks the content of the manual once, at product level. All seven sections are REQUIRED. If one section is missing, the manual scores 0% (all-or-nothing).
 </t>
         </is>
       </c>
       <c r="E11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check the table of contents and the body of the manual for each of the 7 sections. Mark each sub-item (↳) below so missing sections are listed.
-All-or-nothing: the criterion scores 100% only if ALL 7 sub-items are Met; if any one is Not Met the score is 0%.
+          <t xml:space="preserve">Check the table of contents and the body of the manual for each of the 7 sections. Mark each sub-item (↳) below, so that the missing sections are listed.
+All-or-nothing: the criterion scores 100% only if all 7 sub-items are Met. If any one sub-item is Not Met, the score is 0%.
 </t>
         </is>
       </c>
@@ -34459,19 +34522,19 @@
       </c>
       <c r="C19" s="172" t="inlineStr">
         <is>
-          <t>Supported FHIR interactions documented per resource (which resources are created, read, updated, searched), e.g. a CapabilityStatement (Connectathon Issue #3)</t>
+          <t>Supported FHIR interactions documented per resource (which resources are created, read, updated, searched), for example a CapabilityStatement (Connectathon Issue #3)</t>
         </is>
       </c>
       <c r="D19" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit a CapabilityStatement (or equivalent) listing each FHIR resource used, its supported interactions (POST, PUT, GET, search) and search parameters.
+          <t xml:space="preserve">Submit a CapabilityStatement (or equivalent) that lists each FHIR resource used, with its supported interactions (POST, PUT, GET, search) and search parameters.
 Purpose: Removes ambiguity about what the system actually sends and receives.
 </t>
         </is>
       </c>
       <c r="E19" s="172" t="inlineStr">
         <is>
-          <t>Check the document lists each resource used in TS1/TS2 with its interactions (POST/PUT/GET/search).</t>
+          <t>Check that the document lists each resource used in TS1/TS2 with its interactions (POST/PUT/GET/search).</t>
         </is>
       </c>
       <c r="F19" s="172" t="inlineStr">
@@ -34550,26 +34613,31 @@
       </c>
       <c r="C20" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">System architecture — integration of the eReferral function with the EMR, judged by how patient details reach the referral (not by how the system is built):
-(a) Fully integrated = 100% — the eReferral function is part of the EMR, OR it is a standalone system integrated with the EMR whose only role is to perform the referral and which receives the patient details automatically;
-(b) Standalone - manual encoding = 50% — the standalone system still requires manual intervention to encode patient details (re-typing, copy-paste or re-upload).
+          <t xml:space="preserve">System architecture: integration of the eReferral function with the EMR, judged by how patient details reach the referral (not by how the system is built).
+(a) Fully integrated = 100%: the eReferral function is part of the EMR. Or, it is a standalone system integrated with the EMR. Its only role is to do the referral, and it receives the patient details automatically.
+(b) Standalone - manual encoding = 50%: the standalone system still needs a person to encode patient details manually (re-typing, copy-paste or re-upload).
 </t>
         </is>
       </c>
       <c r="D20" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit a system architecture diagram showing the EMR, the eReferral function (built-in or a separate system) and how patient details flow from the EMR record into the referral. A high-level diagram is sufficient — internal component, network or infrastructure details are not required. Any integration method is acceptable (shared database, API, FHIR, HL7 v2, other interface).
-Evidence options (vendor's choice — any ONE that proves compliance): (a) the full document / configuration; (b) a high-level or redacted version plus a signed attestation by an authorized officer that the control meets the referenced TB items; (c) independent certification or report (e.g., ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter); or (d) a view-only presentation (screen share or on site) recorded by the Validators as "sighted" with date, without keeping a copy. Source code, keys, credentials and internal network details are never required. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
-Purpose: What matters is that patient details recorded once in the EMR are reused without manual re-encoding. Whether the eReferral function is built into the EMR or is a separate system is the vendor's design choice and is not penalised.
+          <t xml:space="preserve">Submit a system architecture diagram. Show the EMR, the eReferral function (built-in or a separate system) and how patient details flow from the EMR record into the referral. A high-level diagram is sufficient. The diagram does not need internal component, network or infrastructure details. The vendor MAY use any integration method (shared database, API, FHIR, HL7 v2, other interface).
+Evidence options: the vendor MAY choose any one option that proves compliance.
+(a) The full document / configuration.
+(b) A high-level or redacted version, plus a signed attestation by an authorized officer that the control meets the referenced TB items.
+(c) Independent certification or report (for example, ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter).
+(d) A view-only presentation (screen share or on site). The Validators record it as "sighted" with the date, and do not keep a copy.
+The vendor never needs to give source code, keys, credentials or internal network details. The evidence is used only for this validation, under the confidentiality undertaking of the Regional Validation Team (Instructions 4B).
+Purpose: The important point is that the system reuses patient details recorded once in the EMR, without manual re-encoding. The vendor MAY build the eReferral function into the EMR or make it a separate system. This design choice gets no penalty.
 </t>
         </is>
       </c>
       <c r="E20" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Review the architecture diagram.
-2. Demonstration: register the Test Data patient in the EMR, then start a referral.
-3. Fully integrated: every patient detail already in the EMR (name, birth date, sex, PhilSys number, PhilHealth ID, address, contact number) appears in the referral without the user re-typing, copy-pasting or re-uploading it — whether the eReferral function is built into the EMR or is a separate system connected to it.
-4. Standalone - manual encoding: any of these details must be encoded manually.
+2. Demonstration: register the Test Data patient in the EMR. Then start a referral.
+3. Fully integrated: every patient detail already in the EMR (name, birth date, sex, PhilSys number, PhilHealth ID, address, contact number) appears in the referral. The user does not re-type, copy-paste or re-upload it. This applies to an eReferral function built into the EMR and to a separate system connected to it.
+4. Standalone - manual encoding: the user has to encode one or more of these details manually.
 5. Not Met: no diagram or no demonstration.
 </t>
         </is>
@@ -34650,27 +34718,35 @@
       </c>
       <c r="C21" s="172" t="inlineStr">
         <is>
-          <t>Product security and privacy design documented and stated against the Technical Baseline and NPC Circular 2023-06: (1) authentication &amp; role-based access, (2) audit logging, (3) encryption in transit and at rest, (4) backup &amp; recovery of data held only in the system (user accounts / credentials, audit trail, configuration), (5) privacy-by-design / privacy-by-default features — data minimisation, retention and secure disposal</t>
+          <t>Product security and privacy design documented and stated against the Technical Baseline and NPC Circular 2023-06: (1) authentication &amp; role-based access, (2) audit logging, (3) encryption in transit and at rest, (4) backup &amp; recovery of data held only in the system (user accounts / credentials, audit trail, configuration), (5) privacy-by-design / privacy-by-default features (data minimisation, retention and secure disposal)</t>
         </is>
       </c>
       <c r="D21" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit security and privacy design documentation covering the five topics. For each topic, state the mechanism used and confirm it meets or exceeds the Technical Baseline (Reference Guide, Ch. 3) (TB-01 to TB-11). Any product, platform or method is acceptable if it meets the baseline. If an equivalent control is used instead, attach a short justification with evidence (Instructions 4A).
-Evidence options (vendor's choice — any ONE that proves compliance): (a) the full document / configuration; (b) a high-level or redacted version plus a signed attestation by an authorized officer that the control meets the referenced TB items; (c) independent certification or report (e.g., ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter); or (d) a view-only presentation (screen share or on site) recorded by the Validators as "sighted" with date, without keeping a copy. Source code, keys, credentials and internal network details are never required. Evidence is used only for this validation, under the Regional Validation Team's confidentiality undertaking (Instructions 4B).
-Purpose: Describes the security features the system provides, in measurable terms. Referral data exchanged is kept on the Shared Health Record; the backup covers data that exists only in the system. Topic 5 also gives facilities (the personal information controllers) what they need for their own Privacy Impact Assessment under NPC Circular 2023-06 §5 and §7.
+          <t xml:space="preserve">Submit security and privacy design documentation that covers the five topics. For each topic, state the mechanism used. Confirm that it meets or exceeds the Technical Baseline (Reference Guide, Ch. 3) (TB-01 to TB-11). The vendor MAY use any product, platform or method that meets the baseline. If the system uses an equivalent control instead, attach a short justification with evidence (Instructions 4A).
+Evidence options: the vendor MAY choose any one option that proves compliance.
+(a) The full document / configuration.
+(b) A high-level or redacted version, plus a signed attestation by an authorized officer that the control meets the referenced TB items.
+(c) Independent certification or report (for example, ISO/IEC 27001, SOC 2, cloud-provider compliance report, penetration-test summary letter).
+(d) A view-only presentation (screen share or on site). The Validators record it as "sighted" with the date, and do not keep a copy.
+The vendor never needs to give source code, keys, credentials or internal network details. The evidence is used only for this validation, under the confidentiality undertaking of the Regional Validation Team (Instructions 4B).
+Purpose: Describes the security features of the system in measurable terms. The Shared Health Record keeps the exchanged referral data. The backup covers data that exists only in the system. Topic 5 also gives facilities (the personal information controllers) the information for their own Privacy Impact Assessment (NPC Circular 2023-06 §5 and §7).
 </t>
         </is>
       </c>
       <c r="E21" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count the five topics. A topic is Met if compliance is shown by ANY accepted evidence option (full or redacted document with signed attestation, independent certification, or view-only presentation recorded as sighted) AND it is mapped to the referenced TB items (or an equivalent control was accepted by the Technical Lead). Record the evidence option used in Notes. Level 2D tests that the controls work.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">Count the five topics. A topic is Met if both conditions are true:
+1. Any accepted evidence option shows compliance (full or redacted document with signed attestation, independent certification, or view-only presentation recorded as sighted).
+2. The topic maps to the referenced TB items (or the Technical Lead accepted an equivalent control).
+Record the evidence option used in Notes. Level 2D tests that the controls work.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
       <c r="F21" s="172" t="inlineStr">
         <is>
-          <t>Security design document, OR redacted summary + signed attestation, OR independent certification, OR view-only presentation</t>
+          <t>Security design document, or redacted summary + signed attestation, or independent certification, or view-only presentation</t>
         </is>
       </c>
       <c r="G21" s="172" t="inlineStr">
@@ -34902,7 +34978,7 @@
       </c>
       <c r="C25" s="193" t="inlineStr">
         <is>
-          <t>Backup &amp; recovery of data held only in the system — user accounts / credentials, audit trail, configuration (TB-09)</t>
+          <t>Backup &amp; recovery of data held only in the system: user accounts / credentials, audit trail, configuration (TB-09)</t>
         </is>
       </c>
       <c r="D25" s="195" t="inlineStr">
@@ -34952,7 +35028,7 @@
       </c>
       <c r="C26" s="193" t="inlineStr">
         <is>
-          <t>Privacy-by-design / privacy-by-default — data minimisation, retention and secure disposal (TB-11; NPC Circular 2023-06 §7–9, §28–30)</t>
+          <t>Privacy-by-design / privacy-by-default: data minimisation, retention and secure disposal (TB-11, NPC Circular 2023-06 §7–9 and §28–30)</t>
         </is>
       </c>
       <c r="D26" s="195" t="inlineStr">
@@ -35007,14 +35083,16 @@
       </c>
       <c r="D27" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit release notes for the version under test and a written timeline for adopting new PH Core / PHeReF IG versions.
-Purpose: Updates to the draft IGs will be applied in a controlled, traceable way.
+          <t xml:space="preserve">Submit release notes for the version under test. Also submit a written timeline for adopting new PH Core / PHeReF IG versions.
+Purpose: The vendor will apply updates to the draft IGs in a controlled, traceable way.
 </t>
         </is>
       </c>
       <c r="E27" s="172" t="inlineStr">
         <is>
-          <t>Check release notes for the version under test and the written update timeline.</t>
+          <t xml:space="preserve">Check the release notes for the version under test.
+Check the written update timeline.
+</t>
         </is>
       </c>
       <c r="F27" s="172" t="inlineStr">
@@ -35142,7 +35220,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -35191,7 +35269,7 @@
     <row r="2" ht="54" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>Before submitting (TS1) or reading (TS2) an eReferral, every coded element must use the official terminology and every registry value or patient identifier must follow the official registry — the exact server, registry or API for each concept is named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4) (SRC-01 to SRC-15). CRITICAL (must be 100%): the IG-required bindings (TS0-01, TS0-02), invalid-code handling (TS0-03), PSGC and NHFR (★ in TS0-06) and the PhilHealth / PhilSys identifiers (TS0-07) — TS1, TS2 and Level 3 cannot work without them. Other items (display text, code-system validity, NHWR, DSWD) carry normal weight but are not critical. How values are obtained (live look-up, scheduled sync or cached copy) is the vendor's choice. Test this part FIRST.</t>
+          <t>Before the EMR submits (TS1) or reads (TS2) an eReferral, every coded element MUST use the official terminology. Every registry value or patient identifier MUST follow the official registry. The Terminology &amp; Registry Sources (Reference Guide, Ch. 4) name the exact server, registry or API for each concept (SRC-01 to SRC-15). The critical items MUST score 100%. They are the IG-required bindings (TS0-01, TS0-02) and invalid-code handling (TS0-03). They also include PSGC and NHFR (★ in TS0-06) and the PhilHealth / PhilSys identifiers (TS0-07). TS1, TS2 and Level 3 cannot work without them. Other items (display text, code-system validity, NHWR, DSWD) have normal weight but are not critical. The vendor MAY choose how to get the values (live look-up, scheduled sync or cached copy). Test this part first.</t>
         </is>
       </c>
     </row>
@@ -35217,7 +35295,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -35399,7 +35477,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="179.5" customHeight="1" s="125">
+    <row r="10" ht="193" customHeight="1" s="125">
       <c r="A10" s="172" t="inlineStr">
         <is>
           <t>TS0-01</t>
@@ -35412,22 +35490,23 @@
       </c>
       <c r="C10" s="172" t="inlineStr">
         <is>
-          <t>PH Core coded elements: values match the official PH Core / base FHIR value sets (required bindings — not locally invented)</t>
+          <t>PH Core coded elements: values match the official PH Core / base FHIR value sets (required bindings, not locally invented)</t>
         </is>
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use the PH Core / base FHIR value sets for each coded field listed (sex, contact point) — source SRC-05. Use the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4) — for coded values, the DOH HIE terminology server (runtime look-up, scheduled sync or cached copy: vendor's choice).
-Purpose: These bindings are REQUIRED in the IG; a wrong code makes the whole referral fail validation (TS1-T.02), so this is critical.
+          <t xml:space="preserve">Use the PH Core / base FHIR value sets for each coded field listed (sex, contact point). The source is SRC-05. Use the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4). For coded values, this source is the DOH HIE terminology server. The vendor MAY choose runtime look-up, scheduled sync or cached copy.
+Purpose: These bindings are REQUIRED in the IG. A wrong code makes the whole referral fail validation (TS1-T.02). Thus this criterion is critical.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Check that the system's configured terminology endpoint is the DOH HIE terminology server (Terminology &amp; Registry Sources — Reference Guide, Ch. 4).
-2. Open each field / dropdown listed as a sub-item and compare the options with the value set on the server ($expand), or check the submitted code ($validate-code).
-3. A sub-item is Met only if every option / submitted code belongs to the bound value set.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+          <t xml:space="preserve">1. Check that the configured terminology endpoint of the system is the DOH HIE terminology server (Terminology &amp; Registry Sources, Reference Guide, Ch. 4).
+2. Open each field / dropdown listed as a sub-item.
+3. Compare the options with the value set on the server ($expand), or check the submitted code ($validate-code).
+4. A sub-item is Met only if every option / submitted code belongs to the bound value set.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -35515,7 +35594,7 @@
       </c>
       <c r="C11" s="193" t="inlineStr">
         <is>
-          <t>Sex — AdministrativeGender (required binding)</t>
+          <t>Sex: AdministrativeGender (required binding)</t>
         </is>
       </c>
       <c r="D11" s="195" t="inlineStr">
@@ -35569,7 +35648,7 @@
       </c>
       <c r="C12" s="193" t="inlineStr">
         <is>
-          <t>Contact number — ContactPointSystem / ContactPointUse (required binding)</t>
+          <t>Contact number: ContactPointSystem / ContactPointUse (required binding)</t>
         </is>
       </c>
       <c r="D12" s="195" t="inlineStr">
@@ -35623,7 +35702,7 @@
       </c>
       <c r="C13" s="193" t="inlineStr">
         <is>
-          <t>Civil status — MaritalStatus value set (required binding in ERefPatient)</t>
+          <t>Civil status: MaritalStatus value set (required binding in ERefPatient)</t>
         </is>
       </c>
       <c r="D13" s="195" t="inlineStr">
@@ -35677,7 +35756,7 @@
       </c>
       <c r="C14" s="193" t="inlineStr">
         <is>
-          <t>Accompanied by / next of kin relationship — RelatedPerson relationship type (required binding on Patient.contact.relationship)</t>
+          <t>Accompanied by / next of kin relationship: RelatedPerson relationship type (required binding on Patient.contact.relationship)</t>
         </is>
       </c>
       <c r="D14" s="195" t="inlineStr">
@@ -35718,7 +35797,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="301" customHeight="1" s="125">
+    <row r="15" ht="341.5" customHeight="1" s="125">
       <c r="A15" s="172" t="inlineStr">
         <is>
           <t>TS0-02</t>
@@ -35736,18 +35815,23 @@
       </c>
       <c r="D15" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use the PHeReF value sets for each coded field — sources SRC-01 to SRC-04 and SRC-09. Use the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4) — for coded values, the DOH HIE terminology server (runtime look-up, scheduled sync or cached copy: vendor's choice).
-Referral Category → ServiceRequest.category (Referral Category VS, SNOMED CT: 73770003 Emergency / 440655000 Outpatient — required). Priority → ServiceRequest.priority (EReferralPriority: routine / urgent / stat — required). Reason for Referral → ServiceRequest.reasonCode (Reason for Referral (Service Type) VS, SNOMED CT). Practitioner Role → PractitionerRole.code (Practitioner Role VS — required). Task status → Task.status (FHIR TaskStatus: requested, received, accepted, rejected, completed).
-Purpose: TS1, TS2 and the Level 3 reports cannot work if these codes are wrong — all five are critical.
+          <t xml:space="preserve">Use the PHeReF value sets for each coded field. The sources are SRC-01 to SRC-04 and SRC-09. Use the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4). For coded values, this source is the DOH HIE terminology server. The vendor MAY choose runtime look-up, scheduled sync or cached copy.
+Referral Category → ServiceRequest.category (Referral Category VS, SNOMED CT: 73770003 Emergency / 440655000 Outpatient, required binding).
+Priority → ServiceRequest.priority (EReferralPriority: routine / urgent / stat, required binding).
+Reason for Referral → ServiceRequest.reasonCode (Reason for Referral (Service Type) VS, SNOMED CT).
+Practitioner Role → PractitionerRole.code (Practitioner Role VS, required binding).
+Task status → Task.status (FHIR TaskStatus: requested, received, accepted, rejected, completed).
+Purpose: TS1, TS2 and the Level 3 reports cannot work if these codes are wrong. All five are critical.
 </t>
         </is>
       </c>
       <c r="E15" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Check that the system's configured terminology endpoint is the DOH HIE terminology server (Terminology &amp; Registry Sources — Reference Guide, Ch. 4).
-2. Open each field / dropdown listed as a sub-item and compare the options with the value set on the server ($expand), or check the submitted code ($validate-code).
-3. A sub-item is Met only if every option / submitted code belongs to the bound value set.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+          <t xml:space="preserve">1. Check that the configured terminology endpoint of the system is the DOH HIE terminology server (Terminology &amp; Registry Sources, Reference Guide, Ch. 4).
+2. Open each field / dropdown listed as a sub-item.
+3. Compare the options with the value set on the server ($expand), or check the submitted code ($validate-code).
+4. A sub-item is Met only if every option / submitted code belongs to the bound value set.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -35835,7 +35919,7 @@
       </c>
       <c r="C16" s="193" t="inlineStr">
         <is>
-          <t>Practitioner Role — PHeReF Practitioner Role VS (required binding)</t>
+          <t>Practitioner Role: PHeReF Practitioner Role VS (required binding)</t>
         </is>
       </c>
       <c r="D16" s="195" t="inlineStr">
@@ -35889,7 +35973,7 @@
       </c>
       <c r="C17" s="193" t="inlineStr">
         <is>
-          <t>Referral Category — PHeReF Referral Category VS, SNOMED CT Emergency / Outpatient (required binding)</t>
+          <t>Referral Category: PHeReF Referral Category VS, SNOMED CT Emergency / Outpatient (required binding)</t>
         </is>
       </c>
       <c r="D17" s="195" t="inlineStr">
@@ -35943,7 +36027,7 @@
       </c>
       <c r="C18" s="193" t="inlineStr">
         <is>
-          <t>Priority — EReferralPriority: routine / urgent / stat (required binding)</t>
+          <t>Priority: EReferralPriority, routine / urgent / stat (required binding)</t>
         </is>
       </c>
       <c r="D18" s="195" t="inlineStr">
@@ -35997,7 +36081,7 @@
       </c>
       <c r="C19" s="193" t="inlineStr">
         <is>
-          <t>Reason for Referral (service type) — PHeReF Reason for Referral VS, SNOMED CT</t>
+          <t>Reason for Referral (service type): PHeReF Reason for Referral VS, SNOMED CT</t>
         </is>
       </c>
       <c r="D19" s="195" t="inlineStr">
@@ -36051,7 +36135,7 @@
       </c>
       <c r="C20" s="193" t="inlineStr">
         <is>
-          <t>Task status — FHIR TaskStatus (requested / received / accepted / rejected / completed)</t>
+          <t>Task status: FHIR TaskStatus (requested / received / accepted / rejected / completed)</t>
         </is>
       </c>
       <c r="D20" s="195" t="inlineStr">
@@ -36092,7 +36176,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="166" customHeight="1" s="125">
+    <row r="21" ht="193" customHeight="1" s="125">
       <c r="A21" s="172" t="inlineStr">
         <is>
           <t>TS0-03</t>
@@ -36105,21 +36189,24 @@
       </c>
       <c r="C21" s="172" t="inlineStr">
         <is>
-          <t>Invalid codes are handled gracefully: the system prevents a code outside the bound value set, OR clearly shows the SHR's rejection to the user and lets them correct and resend (Connectathon Issue #25)</t>
+          <t>Invalid codes are handled gracefully: the system prevents a code outside the bound value set, or it clearly shows the SHR's rejection to the user and lets the user correct and resend (Connectathon Issue #25)</t>
         </is>
       </c>
       <c r="D21" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Either (a) validate coded fields before saving / sending (e.g., pick-lists built from the value set, $validate-code) so an out-of-value-set code cannot be entered, or (b) when the SHR rejects the referral, show the user a clear error naming the field and allow correction and resend. Which approach is used is the vendor's choice.
-Purpose: Wrong codes never silently enter the referral or the dashboards, and users are never left with a failed referral they cannot see.
+          <t xml:space="preserve">Use approach (a) or approach (b). The vendor MAY choose the approach.
+(a) Validate coded fields before saving / sending (for example, pick-lists built from the value set, $validate-code). Then a user cannot enter an out-of-value-set code.
+(b) When the SHR rejects the referral, show the user a clear error that names the field. Let the user correct the referral and resend it.
+Purpose: Wrong codes never silently enter the referral or the dashboards. Users never have a failed referral that they cannot see.
 </t>
         </is>
       </c>
       <c r="E21" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validator (server-side) attempts to submit one code outside the value set (e.g., for Reason for Referral).
-Met if EITHER the EMR blocks / flags it before sending, OR the EMR displays the SHR's rejection in understandable terms and the user can correct and resend successfully.
-Not Met if the error is not shown to the user, or the code is accepted.
+          <t xml:space="preserve">The Validator (server-side) tries to submit one code outside the value set (for example, for Reason for Referral).
+Met if the EMR blocks / flags the code before sending.
+Also Met if the EMR shows the SHR's rejection in understandable terms, and the user can correct and resend successfully.
+Not Met if the EMR does not show the error to the user, or if the code is accepted.
 </t>
         </is>
       </c>
@@ -36199,20 +36286,20 @@
       </c>
       <c r="C22" s="172" t="inlineStr">
         <is>
-          <t>Codes are displayed with their official display text (no locally renamed labels)</t>
+          <t>Codes are shown with their official display text (no locally renamed labels)</t>
         </is>
       </c>
       <c r="D22" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Display the official display text from the terminology server; do not rename code labels locally. A local translation may be shown in addition to, not instead of, the official text.
+          <t xml:space="preserve">Show the official display text from the terminology server. Do not rename code labels locally. The EMR MAY show a local translation in addition to the official text, but not instead of it.
 Purpose: Everyone sees the same meaning for the same code.
 </t>
         </is>
       </c>
       <c r="E22" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compare displayed labels for 3 value sets against the terminology server display. Count matching value sets.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+          <t xml:space="preserve">Compare the labels that the EMR shows for 3 value sets with the terminology server display. Count the value sets that match.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -36300,7 +36387,7 @@
       </c>
       <c r="C23" s="193" t="inlineStr">
         <is>
-          <t>Practitioner Role — official display text</t>
+          <t>Practitioner Role: official display text</t>
         </is>
       </c>
       <c r="D23" s="195" t="inlineStr">
@@ -36350,7 +36437,7 @@
       </c>
       <c r="C24" s="193" t="inlineStr">
         <is>
-          <t>Referral Category — official display text</t>
+          <t>Referral Category: official display text</t>
         </is>
       </c>
       <c r="D24" s="195" t="inlineStr">
@@ -36400,7 +36487,7 @@
       </c>
       <c r="C25" s="193" t="inlineStr">
         <is>
-          <t>Reason for Referral — official display text</t>
+          <t>Reason for Referral: official display text</t>
         </is>
       </c>
       <c r="D25" s="195" t="inlineStr">
@@ -36437,7 +36524,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="139" customHeight="1" s="125">
+    <row r="26" ht="152.5" customHeight="1" s="125">
       <c r="A26" s="172" t="inlineStr">
         <is>
           <t>TS0-05</t>
@@ -36450,20 +36537,20 @@
       </c>
       <c r="C26" s="172" t="inlineStr">
         <is>
-          <t>International code systems used where the PH Core / PHeReF IG binds them are valid codes on the DOH terminology server: SNOMED CT, LOINC and ICD-10</t>
+          <t>Codes from international code systems (where the PH Core / PHeReF IG binds them) are valid on the DOH terminology server: SNOMED CT, LOINC and ICD-10</t>
         </is>
       </c>
       <c r="D26" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where the IG binds a field to SNOMED CT (practitioner role, referral category, reason for referral) or LOINC (vital-sign Observation codes), or ICD-10 (working impression, where bound), send codes that exist in the edition loaded on the DOH terminology server, with the correct system URI.
+          <t xml:space="preserve">The IG binds some fields to SNOMED CT (practitioner role, referral category, reason for referral), LOINC (vital-sign Observation codes) or ICD-10 (working impression, where bound). For these fields, send codes that exist in the edition loaded on the DOH terminology server. Use the correct system URI.
 Purpose: Codes are valid and comparable across facilities.
 </t>
         </is>
       </c>
       <c r="E26" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validator (server-side) runs CodeSystem/$validate-code on the DOH terminology server (or $validate on the submitted bundle) for every SNOMED CT, LOINC and ICD-10 code in the Test Data referral. A sub-item is Met only if every code of that system is valid.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+          <t xml:space="preserve">The Validator (server-side) checks every SNOMED CT, LOINC and ICD-10 code in the Test Data referral. The check uses CodeSystem/$validate-code on the DOH terminology server (or $validate on the submitted bundle). A sub-item is Met only if every code of that system is valid.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -36551,7 +36638,7 @@
       </c>
       <c r="C27" s="193" t="inlineStr">
         <is>
-          <t>SNOMED CT — codes valid; system = http://snomed.info/sct</t>
+          <t>SNOMED CT: codes valid, system = http://snomed.info/sct</t>
         </is>
       </c>
       <c r="D27" s="195" t="inlineStr">
@@ -36601,7 +36688,7 @@
       </c>
       <c r="C28" s="193" t="inlineStr">
         <is>
-          <t>LOINC — vital-sign codes valid; system = http://loinc.org</t>
+          <t>LOINC: vital-sign codes valid, system = http://loinc.org</t>
         </is>
       </c>
       <c r="D28" s="195" t="inlineStr">
@@ -36651,7 +36738,7 @@
       </c>
       <c r="C29" s="193" t="inlineStr">
         <is>
-          <t>ICD-10 — working-impression codes valid; system = http://hl7.org/fhir/sid/icd-10 (N/A if not bound)</t>
+          <t>ICD-10: working-impression codes valid, system = http://hl7.org/fhir/sid/icd-10 (N/A if not bound)</t>
         </is>
       </c>
       <c r="D29" s="195" t="inlineStr">
@@ -36688,7 +36775,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="179.5" customHeight="1" s="125">
+    <row r="30" ht="206.5" customHeight="1" s="125">
       <c r="A30" s="172" t="inlineStr">
         <is>
           <t>TS0-06</t>
@@ -36706,17 +36793,18 @@
       </c>
       <c r="D30" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Take PSGC codes from the PSA PSGC release announced by the DOH (SRC-10), facility codes from the NHFR (SRC-11) and practitioner identifiers from the NHWR / PRC (SRC-12). How the registry is accessed (API, scheduled sync or official download) is the vendor's choice; the release must match the DOH server.
-Purpose: PSGC and NHFR are critical — the receiving facility finds its referrals by NHFR code (TS2-01) and the Level 3 reports group by facility and municipality.
+          <t xml:space="preserve">Take PSGC codes from the PSA PSGC release that the DOH announced (SRC-10). Take facility codes from the NHFR (SRC-11). Take practitioner identifiers from the NHWR / PRC (SRC-12). The vendor MAY choose how to access the registry (API, scheduled sync or official download). The release MUST match the DOH server.
+Purpose: PSGC and NHFR are critical. The receiving facility finds its referrals by NHFR code (TS2-01). The Level 3 reports group by facility and municipality.
 </t>
         </is>
       </c>
       <c r="E30" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open each field listed as a sub-item and compare the values with the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4).
-2. Server-side check: confirm the submitted codes exist in that registry / the DOH terminology server.
-3. For NHFR (TS0-06.2): try to type a facility that is not in the NHFR — the system must only allow selecting NHFR facilities (absorbs Rev 6 L4-09).
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+          <t xml:space="preserve">1. Open each field listed as a sub-item.
+2. Compare the values with the source named in the Terminology &amp; Registry Sources (Reference Guide, Ch. 4).
+3. Server-side check: confirm that the submitted codes exist in that registry / the DOH terminology server.
+4. For NHFR (TS0-06.2): try to type a facility that is not in the NHFR. The system MUST allow the user to select only NHFR facilities (absorbs Rev 6 L4-09).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -36804,7 +36892,7 @@
       </c>
       <c r="C31" s="193" t="inlineStr">
         <is>
-          <t>PSGC code — Philippine Standard Geographic Code (PSA)</t>
+          <t>PSGC code: Philippine Standard Geographic Code (PSA)</t>
         </is>
       </c>
       <c r="D31" s="195" t="inlineStr">
@@ -36858,7 +36946,7 @@
       </c>
       <c r="C32" s="193" t="inlineStr">
         <is>
-          <t>NHFR code — National Health Facility Registry; facilities selected only from the NHFR, not free-typed (absorbs Rev 6 L4-09)</t>
+          <t>NHFR code: National Health Facility Registry. Facilities are selected only from the NHFR, not free-typed (absorbs Rev 6 L4-09)</t>
         </is>
       </c>
       <c r="D32" s="195" t="inlineStr">
@@ -36912,7 +37000,7 @@
       </c>
       <c r="C33" s="193" t="inlineStr">
         <is>
-          <t>NHWR — health worker identifier / licence no. (National Health Workforce Registry)</t>
+          <t>NHWR: health worker identifier / licence no. (National Health Workforce Registry)</t>
         </is>
       </c>
       <c r="D33" s="195" t="inlineStr">
@@ -36949,7 +37037,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="301" customHeight="1" s="125">
+    <row r="34" ht="341.5" customHeight="1" s="125">
       <c r="A34" s="172" t="inlineStr">
         <is>
           <t>TS0-07</t>
@@ -36962,24 +37050,30 @@
       </c>
       <c r="C34" s="172" t="inlineStr">
         <is>
-          <t>Patient identifiers — PhilHealth ID and PhilSys number — are captured, validated and sent with the official PH Core identifier system, so that every patient record is linked to them (CRITICAL)</t>
+          <t>Patient identifiers (PhilHealth ID and PhilSys number) are captured, validated and sent with the official PH Core identifier system, so that every patient record is linked to them (critical)</t>
         </is>
       </c>
       <c r="D34" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">For every patient: (1) provide fields for the PhilHealth ID and the PhilSys number; (2) validate the format per the PH Core IG and reject malformed values; (3) send each as Patient.identifier with the PH Core identifier system (PHCorePhilHealthID / PHCorePhilSysID); (4) where a verification service is made available for the sandbox — e.g., the PhilSys Verifier through the DSWD dxCLOUD API under an agreement with DSWD (SRC-14), or a PhilHealth service (SRC-13) — use it. If a patient genuinely has no number yet, the record may be saved with the reason recorded (e.g., "not yet registered") so it can be linked later — the system must never invent or default a number. How validation is implemented is the vendor's choice.
-Purpose: Patients are expected to be linked to their PhilHealth and PhilSys numbers across the network; these identifiers are the keys for matching records and avoiding duplicates (L4-08).
+          <t xml:space="preserve">For every patient:
+(1) Provide fields for the PhilHealth ID and the PhilSys number.
+(2) Validate the format per the PH Core IG. Reject malformed values.
+(3) Send each identifier as Patient.identifier with the PH Core identifier system (PHCorePhilHealthID / PHCorePhilSysID).
+(4) Use a verification service where one is made available for the sandbox. Examples: the PhilSys Verifier through the DSWD dxCLOUD API under an agreement with DSWD (SRC-14), or a PhilHealth service (SRC-13).
+If a patient genuinely has no number yet, the system MAY save the record with the reason recorded (for example, "not yet registered"). Then the record can be linked later. The system MUST NOT invent or default a number. The vendor MAY choose how to implement validation.
+Purpose: Patients are expected to be linked to their PhilHealth and PhilSys numbers across the network. These identifiers are the keys for matching records and avoiding duplicates (L4-08).
 </t>
         </is>
       </c>
       <c r="E34" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">For EACH identifier (sub-item):
-1. Enter the Test Data value and submit; Validator (server-side) retrieves the Patient and confirms identifier.system and value match PH Core and the Test Data.
-2. Enter one malformed value (e.g., wrong number of digits, or letters); the system must reject it.
-3. If a verification service is available on the sandbox, confirm the system used it.
-Met only if all applicable steps pass. CRITICAL — both sub-items must be Met.
-Mark each sub-item (↳) below; Achieved is counted automatically.
+          <t xml:space="preserve">For each identifier (sub-item):
+1. Enter the Test Data value and submit it.
+2. Validator (server-side): retrieve the Patient. Confirm that identifier.system and value match PH Core and the Test Data.
+3. Enter one malformed value (for example, wrong number of digits, or letters). The system MUST reject it.
+4. If a verification service is available on the sandbox, confirm that the system used it.
+Met only if all applicable steps pass. Critical: both sub-items MUST be Met.
+Mark each sub-item (↳) below. The tool counts Achieved automatically.
 </t>
         </is>
       </c>
@@ -37067,7 +37161,7 @@
       </c>
       <c r="C35" s="193" t="inlineStr">
         <is>
-          <t>PhilHealth ID (PhilHealth) — official identifier system, format validated, malformed value rejected</t>
+          <t>PhilHealth ID (PhilHealth): official identifier system, format validated, malformed value rejected</t>
         </is>
       </c>
       <c r="D35" s="195" t="inlineStr">
@@ -37121,7 +37215,7 @@
       </c>
       <c r="C36" s="193" t="inlineStr">
         <is>
-          <t>PhilSys number (PSA) — official identifier system, format validated, malformed value rejected</t>
+          <t>PhilSys number (PSA): official identifier system, format validated, malformed value rejected</t>
         </is>
       </c>
       <c r="D36" s="195" t="inlineStr">
@@ -37162,7 +37256,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="125.5" customHeight="1" s="125">
+    <row r="37" ht="152.5" customHeight="1" s="125">
       <c r="A37" s="172" t="inlineStr">
         <is>
           <t>TS0-08</t>
@@ -37175,17 +37269,20 @@
       </c>
       <c r="C37" s="172" t="inlineStr">
         <is>
-          <t>OPTIONAL — DSWD household / beneficiary identifier (Household No. or UBD ID) can be recorded and, where DSWD grants API access, looked up through the DSWD dxCLOUD API (SRC-15)</t>
+          <t>OPTIONAL: DSWD household / beneficiary identifier (Household No. or UBD ID) can be recorded and, where DSWD grants API access, queried through the DSWD dxCLOUD API (SRC-15)</t>
         </is>
       </c>
       <c r="D37" s="172" t="inlineStr">
         <is>
-          <t>Provide a field for the DSWD household / beneficiary identifier. Where DSWD has granted API access and a data sharing agreement is in place, the system may look it up or verify it through the DSWD dxCLOUD API (https://dxcloud.dswd.gov.ph/api/documentation — e.g., /api/person/getUBID, /api/person/verifyPantawid). Optional and not scored until the TDG defines the PH Core / PHeReF mapping.</t>
+          <t xml:space="preserve">Provide a field for the DSWD household / beneficiary identifier. The system MAY query or verify the identifier through the DSWD dxCLOUD API. This applies only where DSWD granted API access and a data sharing agreement is in place. See https://dxcloud.dswd.gov.ph/api/documentation (for example, /api/person/getUBID, /api/person/verifyPantawid). This item is OPTIONAL and is not scored until the TDG defines the PH Core / PHeReF mapping.
+</t>
         </is>
       </c>
       <c r="E37" s="172" t="inlineStr">
         <is>
-          <t>Record whether the field exists and, if DSWD API access was granted, whether a look-up works (for information only).</t>
+          <t xml:space="preserve">Record whether the field exists.
+If DSWD granted API access, record whether a look-up works (for information only).
+</t>
         </is>
       </c>
       <c r="F37" s="172" t="inlineStr">
@@ -37310,7 +37407,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -37359,7 +37456,7 @@
     <row r="2" ht="48" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>The referring facility submits the Test Data referral to the Shared Health Record (SHR). Every item is verified ON THE SERVER using any one form of server-side evidence: an Interoperability Layer log (e.g., OpenHIM), an Inferno / FHIR validator report, or the raw request / response payload from the developer. Fields are grouped by FHIR resource — open the resource once and tick its fields. ★ marks critical sub-items. How the data is sent (HTTP verbs, bundle style) is the vendor's choice.</t>
+          <t>The referring facility submits the Test Data referral to the Shared Health Record (SHR). The Validator verifies every item on the server with any one form of server-side evidence. Accepted forms: an Interoperability Layer log (for example, OpenHIM), an Inferno / FHIR validator report, or the raw request / response payload from the developer. Fields are grouped by FHIR resource. Open the resource once and tick its fields. ★ marks critical sub-items. The vendor MAY choose how to send the data (HTTP verbs, bundle style).</t>
         </is>
       </c>
     </row>
@@ -37385,7 +37482,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -37567,7 +37664,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="233.5" customHeight="1" s="125">
+    <row r="10" ht="260.5" customHeight="1" s="125">
       <c r="A10" s="172" t="inlineStr">
         <is>
           <t>TS1-01</t>
@@ -37585,20 +37682,25 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Organization (referring facility) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Organization.name; Organization.identifier (NHFR; HCPN); Organization.address (PSGC-coded); Organization.telecom
-Source: SRC-10, SRC-11, SRC-05 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Organization (referring facility), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Organization.name, Organization.identifier (NHFR, HCPN), Organization.address (PSGC-coded), Organization.telecom
+Source: SRC-10, SRC-11, SRC-05 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: The receiving facility knows exactly where the patient comes from.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Organization in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Organization in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -37686,7 +37788,7 @@
       </c>
       <c r="C11" s="193" t="inlineStr">
         <is>
-          <t>HCPN name — Organization.identifier (HCPN)</t>
+          <t>HCPN name: Organization.identifier (HCPN)</t>
         </is>
       </c>
       <c r="D11" s="195" t="inlineStr">
@@ -37736,7 +37838,7 @@
       </c>
       <c r="C12" s="193" t="inlineStr">
         <is>
-          <t>Facility name — Organization.name</t>
+          <t>Facility name: Organization.name</t>
         </is>
       </c>
       <c r="D12" s="195" t="inlineStr">
@@ -37786,7 +37888,7 @@
       </c>
       <c r="C13" s="193" t="inlineStr">
         <is>
-          <t>NHFR code — Organization.identifier (NHFR)</t>
+          <t>NHFR code: Organization.identifier (NHFR)</t>
         </is>
       </c>
       <c r="D13" s="195" t="inlineStr">
@@ -37840,7 +37942,7 @@
       </c>
       <c r="C14" s="193" t="inlineStr">
         <is>
-          <t>Address, PSGC-coded — Organization.address</t>
+          <t>Address, PSGC-coded: Organization.address</t>
         </is>
       </c>
       <c r="D14" s="195" t="inlineStr">
@@ -37890,7 +37992,7 @@
       </c>
       <c r="C15" s="193" t="inlineStr">
         <is>
-          <t>Contact number — Organization.telecom</t>
+          <t>Contact number: Organization.telecom</t>
         </is>
       </c>
       <c r="D15" s="195" t="inlineStr">
@@ -37927,7 +38029,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="247" customHeight="1" s="125">
+    <row r="16" ht="274" customHeight="1" s="125">
       <c r="A16" s="172" t="inlineStr">
         <is>
           <t>TS1-02</t>
@@ -37945,20 +38047,25 @@
       </c>
       <c r="D16" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Organization (receiving facility) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Organization.name; Organization.identifier (NHFR); Organization.address — referenced from ServiceRequest.performer / Task.owner
-Source: SRC-10, SRC-11 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
-Purpose: The referral is addressed to the right facility so it appears in that facility's incoming list.
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Organization (receiving facility), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Organization.name, Organization.identifier (NHFR), Organization.address. The Organization is referenced from ServiceRequest.performer / Task.owner.
+Source: SRC-10, SRC-11 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
+Purpose: The referral is addressed to the correct facility, so it appears in the incoming list of that facility.
 </t>
         </is>
       </c>
       <c r="E16" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Organization in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Organization in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -38046,7 +38153,7 @@
       </c>
       <c r="C17" s="193" t="inlineStr">
         <is>
-          <t>Facility name — Organization.name</t>
+          <t>Facility name: Organization.name</t>
         </is>
       </c>
       <c r="D17" s="195" t="inlineStr">
@@ -38096,7 +38203,7 @@
       </c>
       <c r="C18" s="193" t="inlineStr">
         <is>
-          <t>NHFR code — Organization.identifier (NHFR)</t>
+          <t>NHFR code: Organization.identifier (NHFR)</t>
         </is>
       </c>
       <c r="D18" s="195" t="inlineStr">
@@ -38150,7 +38257,7 @@
       </c>
       <c r="C19" s="193" t="inlineStr">
         <is>
-          <t>Address, PSGC-coded — Organization.address</t>
+          <t>Address, PSGC-coded: Organization.address</t>
         </is>
       </c>
       <c r="D19" s="195" t="inlineStr">
@@ -38187,7 +38294,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="274" customHeight="1" s="125">
+    <row r="20" ht="314.5" customHeight="1" s="125">
       <c r="A20" s="172" t="inlineStr">
         <is>
           <t>TS1-03</t>
@@ -38205,20 +38312,25 @@
       </c>
       <c r="D20" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the PractitionerRole + Practitioner (referring facility) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Practitioner.name; PractitionerRole.code (Practitioner Role VS); referenced by ServiceRequest.requester and Task.requester. A care navigator at the referring facility, where assigned, is a separate PractitionerRole (role code from the Practitioner Role VS).
-Source: SRC-01, SRC-12 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the PractitionerRole + Practitioner (referring facility), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Practitioner.name, PractitionerRole.code (Practitioner Role VS). The PractitionerRole is referenced by ServiceRequest.requester and Task.requester. A care navigator at the referring facility, where assigned, is a separate PractitionerRole (role code from the Practitioner Role VS).
+Source: SRC-01, SRC-12 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: The receiving facility knows who is accountable for the referral and whom to call back.
 </t>
         </is>
       </c>
       <c r="E20" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the PractitionerRole + Practitioner in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the PractitionerRole + Practitioner in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -38306,7 +38418,7 @@
       </c>
       <c r="C21" s="193" t="inlineStr">
         <is>
-          <t>Name of referring practitioner — Practitioner.name</t>
+          <t>Name of referring practitioner: Practitioner.name</t>
         </is>
       </c>
       <c r="D21" s="195" t="inlineStr">
@@ -38356,7 +38468,7 @@
       </c>
       <c r="C22" s="193" t="inlineStr">
         <is>
-          <t>Practitioner role — PractitionerRole.code</t>
+          <t>Practitioner role: PractitionerRole.code</t>
         </is>
       </c>
       <c r="D22" s="195" t="inlineStr">
@@ -38410,7 +38522,7 @@
       </c>
       <c r="C23" s="193" t="inlineStr">
         <is>
-          <t>Care navigator at the referring facility, if assigned — separate PractitionerRole (N/A if the facility does not assign one)</t>
+          <t>Care navigator at the referring facility, if assigned: separate PractitionerRole (N/A if the facility does not assign one)</t>
         </is>
       </c>
       <c r="D23" s="195" t="inlineStr">
@@ -38501,7 +38613,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="287.5" customHeight="1" s="125">
+    <row r="25" ht="301" customHeight="1" s="125">
       <c r="A25" s="172" t="inlineStr">
         <is>
           <t>TS1-04</t>
@@ -38519,20 +38631,25 @@
       </c>
       <c r="D25" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Patient (ERefPatient / PH Core Patient) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Patient.name; Patient.identifier (PH Core PhilSys and PhilHealth slices); Patient.birthDate; Patient.gender; Patient.maritalStatus; Patient.address (PSGC-coded); Patient.telecom; PWD Disability Registration extension. Age is NOT sent — the receiving system computes it from birthDate (checked in TS2-04).
-Source: SRC-05, SRC-10, SRC-13, SRC-14 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Patient (ERefPatient / PH Core Patient), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Patient.name, Patient.identifier (PH Core PhilSys and PhilHealth slices), Patient.birthDate, Patient.gender. Also Patient.maritalStatus, Patient.address (PSGC-coded), Patient.telecom, PWD Disability Registration extension. The EMR does not send age. The receiving system computes it from birthDate (checked in TS2-04).
+Source: SRC-05, SRC-10, SRC-13, SRC-14 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: The patient is identified unambiguously across facilities.
 </t>
         </is>
       </c>
       <c r="E25" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Patient in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Patient in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -38620,7 +38737,7 @@
       </c>
       <c r="C26" s="193" t="inlineStr">
         <is>
-          <t>Full name — Patient.name</t>
+          <t>Full name: Patient.name</t>
         </is>
       </c>
       <c r="D26" s="195" t="inlineStr">
@@ -38670,7 +38787,7 @@
       </c>
       <c r="C27" s="193" t="inlineStr">
         <is>
-          <t>PhilSys number — Patient.identifier (PH Core PhilSys system)</t>
+          <t>PhilSys number: Patient.identifier (PH Core PhilSys system)</t>
         </is>
       </c>
       <c r="D27" s="195" t="inlineStr">
@@ -38724,7 +38841,7 @@
       </c>
       <c r="C28" s="193" t="inlineStr">
         <is>
-          <t>PhilHealth ID — Patient.identifier (PH Core PhilHealth system)</t>
+          <t>PhilHealth ID: Patient.identifier (PH Core PhilHealth system)</t>
         </is>
       </c>
       <c r="D28" s="195" t="inlineStr">
@@ -38778,7 +38895,7 @@
       </c>
       <c r="C29" s="193" t="inlineStr">
         <is>
-          <t>Birth date — Patient.birthDate</t>
+          <t>Birth date: Patient.birthDate</t>
         </is>
       </c>
       <c r="D29" s="195" t="inlineStr">
@@ -38828,7 +38945,7 @@
       </c>
       <c r="C30" s="193" t="inlineStr">
         <is>
-          <t>Sex — Patient.gender</t>
+          <t>Sex: Patient.gender</t>
         </is>
       </c>
       <c r="D30" s="195" t="inlineStr">
@@ -38882,7 +38999,7 @@
       </c>
       <c r="C31" s="193" t="inlineStr">
         <is>
-          <t>Civil status — Patient.maritalStatus</t>
+          <t>Civil status: Patient.maritalStatus</t>
         </is>
       </c>
       <c r="D31" s="195" t="inlineStr">
@@ -38932,7 +39049,7 @@
       </c>
       <c r="C32" s="193" t="inlineStr">
         <is>
-          <t>Address, PSGC-coded — Patient.address</t>
+          <t>Address, PSGC-coded: Patient.address</t>
         </is>
       </c>
       <c r="D32" s="195" t="inlineStr">
@@ -38982,7 +39099,7 @@
       </c>
       <c r="C33" s="193" t="inlineStr">
         <is>
-          <t>Contact number — Patient.telecom</t>
+          <t>Contact number: Patient.telecom</t>
         </is>
       </c>
       <c r="D33" s="195" t="inlineStr">
@@ -39032,7 +39149,7 @@
       </c>
       <c r="C34" s="193" t="inlineStr">
         <is>
-          <t>PWD registration — PWD Disability Registration extension (N/A if the test patient has none)</t>
+          <t>PWD registration: PWD Disability Registration extension (N/A if the test patient has none)</t>
         </is>
       </c>
       <c r="D34" s="195" t="inlineStr">
@@ -39069,7 +39186,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="206.5" customHeight="1" s="125">
+    <row r="35" ht="220" customHeight="1" s="125">
       <c r="A35" s="172" t="inlineStr">
         <is>
           <t>TS1-05</t>
@@ -39087,17 +39204,22 @@
       </c>
       <c r="D35" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send the accompanying person / next of kin (name, relationship, contact number) as a RelatedPerson (ERefRelatedPerson) per the IG. Patient.contact is accepted as an equivalent while the IG is in draft, provided the values are complete and pass $validate. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
+          <t xml:space="preserve">Send the accompanying person / next of kin (name, relationship, contact number) as a RelatedPerson (ERefRelatedPerson), in accordance with the IG. While the IG is in draft, the vendor MAY use Patient.contact as an equivalent, if the values are complete and pass $validate. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
 Purpose: The receiving facility knows who is with the patient and whom to contact.
 </t>
         </is>
       </c>
       <c r="E35" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data value and submit.
-2. In the server-side evidence, find the RelatedPerson (or Patient.contact) and compare name, relationship and contact number with the Test Data.
+          <t xml:space="preserve">1. Enter the Test Data value.
+2. Submit the referral.
+3. In the server-side evidence, find the RelatedPerson (or Patient.contact).
+4. Compare name, relationship and contact number with the Test Data.
 Met only if all three match.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -39164,7 +39286,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="287.5" customHeight="1" s="125">
+    <row r="36" ht="301" customHeight="1" s="125">
       <c r="A36" s="172" t="inlineStr">
         <is>
           <t>TS1-06</t>
@@ -39182,20 +39304,25 @@
       </c>
       <c r="D36" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the ServiceRequest (EReferral ServiceRequest) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: ServiceRequest.authoredOn; .category (Referral Category VS); .priority (EReferralPriority); .reasonCode (Reason for Referral VS) with .reasonReference → Condition; .subject → Patient; .requester → referring PractitionerRole; .performer → receiving facility / practitioner; .intent = order (fixed); .status.
-Source: SRC-02, SRC-03, SRC-09 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the ServiceRequest (EReferral ServiceRequest), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: ServiceRequest.authoredOn, .category (Referral Category VS), .priority (EReferralPriority), .reasonCode (Reason for Referral VS) with .reasonReference → Condition. Links: .subject → Patient, .requester → referring PractitionerRole, .performer → receiving facility / practitioner. Also .intent = order (fixed) and .status.
+Source: SRC-02, SRC-03, SRC-09 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: The receiving facility sees what is requested, how urgent it is and why.
 </t>
         </is>
       </c>
       <c r="E36" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the ServiceRequest in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the ServiceRequest in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -39283,7 +39410,7 @@
       </c>
       <c r="C37" s="193" t="inlineStr">
         <is>
-          <t>Date of referral — ServiceRequest.authoredOn</t>
+          <t>Date of referral: ServiceRequest.authoredOn</t>
         </is>
       </c>
       <c r="D37" s="195" t="inlineStr">
@@ -39333,7 +39460,7 @@
       </c>
       <c r="C38" s="193" t="inlineStr">
         <is>
-          <t>Referral category — ServiceRequest.category (Emergency / Outpatient)</t>
+          <t>Referral category: ServiceRequest.category (Emergency / Outpatient)</t>
         </is>
       </c>
       <c r="D38" s="195" t="inlineStr">
@@ -39387,7 +39514,7 @@
       </c>
       <c r="C39" s="193" t="inlineStr">
         <is>
-          <t>Priority — ServiceRequest.priority (routine / urgent / stat)</t>
+          <t>Priority: ServiceRequest.priority (routine / urgent / stat)</t>
         </is>
       </c>
       <c r="D39" s="195" t="inlineStr">
@@ -39441,7 +39568,7 @@
       </c>
       <c r="C40" s="193" t="inlineStr">
         <is>
-          <t>Reason for referral — ServiceRequest.reasonCode</t>
+          <t>Reason for referral: ServiceRequest.reasonCode</t>
         </is>
       </c>
       <c r="D40" s="195" t="inlineStr">
@@ -39495,7 +39622,7 @@
       </c>
       <c r="C41" s="193" t="inlineStr">
         <is>
-          <t>Links — subject → Patient, requester → referring PractitionerRole, performer → receiving facility</t>
+          <t>Links: subject → Patient, requester → referring PractitionerRole, performer → receiving facility</t>
         </is>
       </c>
       <c r="D41" s="195" t="inlineStr">
@@ -39549,7 +39676,7 @@
       </c>
       <c r="C42" s="193" t="inlineStr">
         <is>
-          <t>Fixed values — intent = order; status per IG</t>
+          <t>Fixed values: intent = order, status as the IG specifies</t>
         </is>
       </c>
       <c r="D42" s="195" t="inlineStr">
@@ -39586,7 +39713,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="274" customHeight="1" s="125">
+    <row r="43" ht="287.5" customHeight="1" s="125">
       <c r="A43" s="172" t="inlineStr">
         <is>
           <t>TS1-07</t>
@@ -39604,20 +39731,25 @@
       </c>
       <c r="D43" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Condition (EReferral Condition) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Chief complaint → Condition.code.text (category problem-list-item); working impression → Condition.code (ICD-10 / SNOMED CT; category encounter-diagnosis), referenced from ServiceRequest.reasonReference; clinical history → Condition.note.
-Source: SRC-06, SRC-08 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Condition (EReferral Condition), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Chief complaint → Condition.code.text (category problem-list-item). Working impression → Condition.code (ICD-10 / SNOMED CT, category encounter-diagnosis), referenced from ServiceRequest.reasonReference. Clinical history → Condition.note.
+Source: SRC-06, SRC-08 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: The receiving clinician understands the clinical reason for the referral.
 </t>
         </is>
       </c>
       <c r="E43" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Condition in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Condition in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -39705,7 +39837,7 @@
       </c>
       <c r="C44" s="193" t="inlineStr">
         <is>
-          <t>Chief complaint — Condition.code.text</t>
+          <t>Chief complaint: Condition.code.text</t>
         </is>
       </c>
       <c r="D44" s="195" t="inlineStr">
@@ -39755,7 +39887,7 @@
       </c>
       <c r="C45" s="193" t="inlineStr">
         <is>
-          <t>Working impression — Condition.code (coded)</t>
+          <t>Working impression: Condition.code (coded)</t>
         </is>
       </c>
       <c r="D45" s="195" t="inlineStr">
@@ -39809,7 +39941,7 @@
       </c>
       <c r="C46" s="193" t="inlineStr">
         <is>
-          <t>Clinical history — Condition.note</t>
+          <t>Clinical history: Condition.note</t>
         </is>
       </c>
       <c r="D46" s="195" t="inlineStr">
@@ -39846,7 +39978,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="260.5" customHeight="1" s="125">
+    <row r="47" ht="274" customHeight="1" s="125">
       <c r="A47" s="172" t="inlineStr">
         <is>
           <t>TS1-08</t>
@@ -39864,20 +39996,25 @@
       </c>
       <c r="D47" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Observation (EReferral Observation) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Observation.code (LOINC), Observation.category = vital-signs, Observation.value[x] with UCUM unit; blood pressure as panel 85354-9 with systolic (8480-6) and diastolic (8462-4) components.
-Source: SRC-07 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Observation (EReferral Observation), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Observation.code (LOINC), Observation.category = vital-signs, Observation.value[x] with UCUM unit. Blood pressure: panel 85354-9 with systolic (8480-6) and diastolic (8462-4) components.
+Source: SRC-07 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
 Purpose: Vital signs are machine-readable and comparable at the receiving facility.
 </t>
         </is>
       </c>
       <c r="E47" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Observation in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Observation in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -39965,7 +40102,7 @@
       </c>
       <c r="C48" s="193" t="inlineStr">
         <is>
-          <t>Blood pressure — panel with systolic and diastolic components</t>
+          <t>Blood pressure: panel with systolic and diastolic components</t>
         </is>
       </c>
       <c r="D48" s="195" t="inlineStr">
@@ -40256,7 +40393,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="152.5" customHeight="1" s="125">
+    <row r="54" ht="166" customHeight="1" s="125">
       <c r="A54" s="172" t="inlineStr">
         <is>
           <t>TS1-09</t>
@@ -40274,15 +40411,18 @@
       </c>
       <c r="D54" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send laboratory results as DiagnosticReport.presentedForm (Attachment with contentType and data or url). Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
+          <t xml:space="preserve">Send laboratory results as DiagnosticReport.presentedForm (Attachment with contentType and data or url). The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
 Purpose: Lab results travel with the patient.
 </t>
         </is>
       </c>
       <c r="E54" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attach the Test Data lab file and submit. Met if the server-side evidence shows a DiagnosticReport whose presentedForm carries the file with a contentType.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Attach the Test Data lab file. Submit the referral. Met if the server-side evidence shows a DiagnosticReport whose presentedForm contains the file with a contentType.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -40349,7 +40489,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="193" customHeight="1" s="125">
+    <row r="55" ht="206.5" customHeight="1" s="125">
       <c r="A55" s="172" t="inlineStr">
         <is>
           <t>TS1-10</t>
@@ -40367,15 +40507,18 @@
       </c>
       <c r="D55" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send the treatment given as MedicationAdministration (EReferral MedicationAdministration) per the IG; Procedure (with note) is accepted as an equivalent for non-drug treatment or while the IG is in draft. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
+          <t xml:space="preserve">Send the treatment given as MedicationAdministration (EReferral MedicationAdministration), in accordance with the IG. For non-drug treatment, or while the IG is in draft, the vendor MAY use Procedure (with note) as an equivalent. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
 Purpose: The receiving facility knows what was already given.
 </t>
         </is>
       </c>
       <c r="E55" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter the Test Data value and submit. Met if the server-side evidence shows the treatment in a MedicationAdministration or Procedure linked to the patient / encounter.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Enter the Test Data value. Submit the referral. Met if the server-side evidence shows the treatment in a MedicationAdministration or Procedure linked to the patient / encounter.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -40442,7 +40585,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="206.5" customHeight="1" s="125">
+    <row r="56" ht="247" customHeight="1" s="125">
       <c r="A56" s="172" t="inlineStr">
         <is>
           <t>TS1-11</t>
@@ -40460,19 +40603,24 @@
       </c>
       <c r="D56" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Provenance (EReferral Provenance) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Provenance.signature; Provenance.recorded; Provenance.target → ServiceRequest.
-Purpose: The referral is attested by an accountable professional.
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Provenance (EReferral Provenance), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Provenance.signature, Provenance.recorded, Provenance.target → ServiceRequest.
+Purpose: An accountable professional attests the referral.
 </t>
         </is>
       </c>
       <c r="E56" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Provenance in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Provenance in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -40560,7 +40708,7 @@
       </c>
       <c r="C57" s="193" t="inlineStr">
         <is>
-          <t>Professional signature — Provenance.signature</t>
+          <t>Professional signature: Provenance.signature</t>
         </is>
       </c>
       <c r="D57" s="195" t="inlineStr">
@@ -40610,7 +40758,7 @@
       </c>
       <c r="C58" s="193" t="inlineStr">
         <is>
-          <t>Date &amp; time of signature — Provenance.recorded</t>
+          <t>Date &amp; time of signature: Provenance.recorded</t>
         </is>
       </c>
       <c r="D58" s="195" t="inlineStr">
@@ -40647,7 +40795,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="260.5" customHeight="1" s="125">
+    <row r="59" ht="287.5" customHeight="1" s="125">
       <c r="A59" s="172" t="inlineStr">
         <is>
           <t>TS1-12</t>
@@ -40665,20 +40813,25 @@
       </c>
       <c r="D59" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capture the fields below in the EMR and send them in the Task (EReferral Task) per the PHeReF / PH Core profile. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-FHIR elements: Task.status = requested; Task.intent = order; Task.focus → ServiceRequest; Task.for → Patient; Task.requester → referring PractitionerRole; Task.owner → receiving facility (or its care navigator, when known); Task.authoredOn.
-Source: SRC-04 (Terminology &amp; Registry Sources — Reference Guide, Ch. 4)
-Purpose: The referral can be tracked; the receiving facility updates this Task (TS2-11).
+          <t xml:space="preserve">Capture the fields below in the EMR. Send them in the Task (EReferral Task), in accordance with the PHeReF / PH Core profile. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+FHIR elements: Task.status = requested, Task.intent = order, Task.focus → ServiceRequest, Task.for → Patient. Also Task.requester → referring PractitionerRole, Task.owner → receiving facility (or its care navigator, when known), Task.authoredOn.
+Source: SRC-04 (Reference Guide, Ch. 4: Terminology &amp; Registry Sources)
+Purpose: The referral can be tracked. The receiving facility updates this Task (TS2-11).
 </t>
         </is>
       </c>
       <c r="E59" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR and submit the referral.
-2. Open the Task in the server-side evidence and compare each sub-item with the Test Data value.
-3. Record the resource ID / log reference in Notes.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">1. Enter the Test Data values for this group (Test Data Section A) in the referring EMR.
+2. Submit the referral.
+3. Open the Task in the server-side evidence.
+4. Compare each sub-item with the Test Data value.
+5. Record the resource ID / log reference in Notes.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -40766,7 +40919,7 @@
       </c>
       <c r="C60" s="193" t="inlineStr">
         <is>
-          <t>Status = requested at submission — Task.status</t>
+          <t>Status = requested at submission: Task.status</t>
         </is>
       </c>
       <c r="D60" s="195" t="inlineStr">
@@ -40820,7 +40973,7 @@
       </c>
       <c r="C61" s="193" t="inlineStr">
         <is>
-          <t>Linked to the referral — Task.focus → ServiceRequest</t>
+          <t>Linked to the referral: Task.focus → ServiceRequest</t>
         </is>
       </c>
       <c r="D61" s="195" t="inlineStr">
@@ -40874,7 +41027,7 @@
       </c>
       <c r="C62" s="193" t="inlineStr">
         <is>
-          <t>Requester = referring practitioner; owner = receiving facility — Task.requester / Task.owner</t>
+          <t>Requester = referring practitioner, owner = receiving facility: Task.requester / Task.owner</t>
         </is>
       </c>
       <c r="D62" s="195" t="inlineStr">
@@ -40924,7 +41077,7 @@
       </c>
       <c r="C63" s="193" t="inlineStr">
         <is>
-          <t>Date / time sent — Task.authoredOn</t>
+          <t>Date / time sent: Task.authoredOn</t>
         </is>
       </c>
       <c r="D63" s="195" t="inlineStr">
@@ -40961,7 +41114,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="166" customHeight="1" s="125">
+    <row r="64" ht="193" customHeight="1" s="125">
       <c r="A64" s="172" t="inlineStr">
         <is>
           <t>TS1-13</t>
@@ -40979,15 +41132,18 @@
       </c>
       <c r="D64" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send the referring-facility encounter as an Encounter (ERefEncounter) and reference it from ServiceRequest.encounter. Any create / update method is accepted (transaction Bundle recommended; conditional create / update allowed) — HTTP verbs are not prescribed. What is tested is that the values reach the SHR in the profiled resource and can be retrieved.
-Purpose: Places the referral in the context of the visit where it was made.
+          <t xml:space="preserve">Send the encounter at the referring facility as an Encounter (ERefEncounter). Reference it from ServiceRequest.encounter. The vendor MAY use any create / update method. A transaction Bundle is RECOMMENDED. The vendor MAY use conditional create / update. This criterion does not prescribe HTTP verbs. The test checks that the values reach the SHR in the profiled resource and that they can be retrieved.
+Purpose: The Encounter puts the referral in the context of the visit where the referral was made.
 </t>
         </is>
       </c>
       <c r="E64" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Met if the server-side evidence shows an Encounter for the test patient, referenced by ServiceRequest.encounter.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -41067,22 +41223,22 @@
       </c>
       <c r="C65" s="172" t="inlineStr">
         <is>
-          <t>Time Called — record whether the EMR captures it (for information)</t>
+          <t>Time Called: record whether the EMR captures it (for information)</t>
         </is>
       </c>
       <c r="D65" s="172" t="inlineStr">
         <is>
-          <t>Capture the field in the EMR. Not scored until the TDG defines its FHIR element (IG v0.1 defines none).</t>
+          <t>Capture the field in the EMR. This criterion is not scored until the TDG defines its FHIR element (IG v0.1 defines none).</t>
         </is>
       </c>
       <c r="E65" s="172" t="inlineStr">
         <is>
-          <t>Record only whether the field exists in the EMR and where it is sent, if anywhere (for information).</t>
+          <t>Record only whether the field exists in the EMR and where the EMR sends it, if anywhere (for information).</t>
         </is>
       </c>
       <c r="F65" s="172" t="inlineStr">
         <is>
-          <t>Screenshot (optional)</t>
+          <t>Screenshot (OPTIONAL)</t>
         </is>
       </c>
       <c r="G65" s="172" t="inlineStr">
@@ -41143,7 +41299,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="44.5" customHeight="1" s="125">
+    <row r="66" ht="58" customHeight="1" s="125">
       <c r="A66" s="172" t="inlineStr">
         <is>
           <t>TS1-15</t>
@@ -41156,12 +41312,12 @@
       </c>
       <c r="C66" s="172" t="inlineStr">
         <is>
-          <t>Mode of transportation (e.g., ambulance, private vehicle) — record whether the EMR captures it (for information)</t>
+          <t>Mode of transportation (for example, ambulance, private vehicle): record whether the EMR captures it (for information)</t>
         </is>
       </c>
       <c r="D66" s="172" t="inlineStr">
         <is>
-          <t>Capture the field in the EMR. Not scored until the TDG defines its FHIR mapping.</t>
+          <t>Capture the field in the EMR. This criterion is not scored until the TDG defines its FHIR mapping.</t>
         </is>
       </c>
       <c r="E66" s="172" t="inlineStr">
@@ -41171,7 +41327,7 @@
       </c>
       <c r="F66" s="172" t="inlineStr">
         <is>
-          <t>Screenshot (optional)</t>
+          <t>Screenshot (OPTIONAL)</t>
         </is>
       </c>
       <c r="G66" s="172" t="inlineStr">
@@ -41232,7 +41388,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="179.5" customHeight="1" s="125">
+    <row r="67" ht="233.5" customHeight="1" s="125">
       <c r="A67" s="172" t="inlineStr">
         <is>
           <t>TS1-16</t>
@@ -41245,21 +41401,24 @@
       </c>
       <c r="C67" s="172" t="inlineStr">
         <is>
-          <t>Submitting a referral for an existing patient reuses the existing Patient record — no duplicate patient is created (moved from L4-08; Connectathon Issue #8)</t>
+          <t>Submitting a referral for an existing patient reuses the existing Patient record: no duplicate patient is created (moved from L4-08, Connectathon Issue #8)</t>
         </is>
       </c>
       <c r="D67" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Match the patient on the SHR by the PH Core PhilSys / PhilHealth identifiers (validated in TS0-07) before creating one — e.g., conditional update 'PUT Patient?identifier=…' as in the IG example transaction (ExampleERefSubmissionBundle), or search then reuse. The matching method is the vendor's choice.
-Purpose: One patient = one record across the network; duplicates split the clinical history.
+          <t xml:space="preserve">Before the EMR creates a Patient, match the patient on the SHR by the PH Core PhilSys / PhilHealth identifiers (validated in TS0-07). For example, use a conditional update 'PUT Patient?identifier=…' as in the IG example transaction (ExampleERefSubmissionBundle). Another example is to search, then reuse the existing Patient. The vendor MAY choose the matching method.
+Purpose: One patient = one record across the network. Duplicates split the clinical history.
 </t>
         </is>
       </c>
       <c r="E67" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit 3 referrals for the same test patient (Test Data Section A identifiers). Validator (server-side) searches Patient by identifier and counts the referrals linked to the single existing Patient.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Submit 3 referrals for the same test patient (Test Data Section A identifiers). The validator (server-side) searches Patient by identifier. The validator counts the referrals linked to the single existing Patient.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -41496,7 +41655,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" ht="125.5" customHeight="1" s="125">
+    <row r="71" ht="152.5" customHeight="1" s="125">
       <c r="A71" s="172" t="inlineStr">
         <is>
           <t>TS1-T.01</t>
@@ -41514,15 +41673,18 @@
       </c>
       <c r="D71" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send the complete referral to the SHR — as one FHIR transaction Bundle (recommended) or by the interactions declared in L1-03 — and handle success and error responses.
+          <t xml:space="preserve">Send the complete referral to the SHR. One FHIR transaction Bundle is RECOMMENDED. As an alternative, the vendor MAY use the interactions declared in L1-03. Handle success responses and error responses.
 Purpose: The whole referral arrives in one piece.
 </t>
         </is>
       </c>
       <c r="E71" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit the Test Data referral; Met if the server-side evidence shows a success response (HTTP 200 / 201) for every resource of the referral.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Submit the Test Data referral. Met if the server-side evidence shows a success response (HTTP 200 / 201) for every resource of the referral.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -41607,14 +41769,14 @@
       </c>
       <c r="D72" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validate outgoing resources against the PHeReF / PH Core profiles (e.g., $validate, the HL7 validator or Inferno) during development until 0 errors.
+          <t xml:space="preserve">During development, validate outgoing resources against the PHeReF / PH Core profiles (for example, $validate, the HL7 validator or Inferno) until there are 0 errors.
 Purpose: The data follows the national standard, not just the vendor's format.
 </t>
         </is>
       </c>
       <c r="E72" s="172" t="inlineStr">
         <is>
-          <t>Run $validate / the official validator / Inferno on the submitted referral (or accept the developer's validator report produced on the same payload during the session). Met only if 0 errors.</t>
+          <t>Run $validate / the official validator / Inferno on the submitted referral. As an alternative, accept the developer's validator report produced on the same payload during the session. Met only if 0 errors.</t>
         </is>
       </c>
       <c r="F72" s="172" t="inlineStr">
@@ -41680,7 +41842,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="85" customHeight="1" s="125">
+    <row r="73" ht="98.5" customHeight="1" s="125">
       <c r="A73" s="172" t="inlineStr">
         <is>
           <t>TS1-T.03</t>
@@ -41699,14 +41861,14 @@
       <c r="D73" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Populate meta.profile of each resource with the canonical URL of its PH Core / PHeReF profile.
-Purpose: Lets the server check the data against the correct rules.
+Purpose: The declared profile lets the server check the data against the correct rules.
 </t>
         </is>
       </c>
       <c r="E73" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Count the resource types in the submitted referral that declare the correct profile.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
 </t>
         </is>
       </c>
@@ -42431,7 +42593,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" ht="139" customHeight="1" s="125">
+    <row r="87" ht="206.5" customHeight="1" s="125">
       <c r="A87" s="172" t="inlineStr">
         <is>
           <t>TS1-T.04</t>
@@ -42449,15 +42611,24 @@
       </c>
       <c r="D87" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">On onward referral: set the Task outcome to referred-onward, create a new ServiceRequest that references the previous one (ServiceRequest.replaces, per IG) and update the previous ServiceRequest status.
-Purpose: Prevents a patient from appearing as referred to two places at once.
+          <t xml:space="preserve">For an onward referral, do these three steps:
+1. Set the Task outcome to referred-onward.
+2. Create a new ServiceRequest that references the previous one (ServiceRequest.replaces, in accordance with the IG).
+3. Update the status of the previous ServiceRequest.
+Purpose: This prevents a patient from appearing as referred to two places at the same time.
 </t>
         </is>
       </c>
       <c r="E87" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perform one onward referral; Met if the server-side evidence shows (1) Task = referred-onward, (2) the new ServiceRequest references the earlier one, and (3) the earlier ServiceRequest status changed.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Do one onward referral. Met if the server-side evidence shows these three items:
+(1) Task = referred-onward.
+(2) The new ServiceRequest references the earlier one.
+(3) The status of the earlier ServiceRequest changed.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -42583,7 +42754,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -42632,7 +42803,7 @@
     <row r="2" ht="48" customHeight="1" s="125">
       <c r="A2" s="174" t="inlineStr">
         <is>
-          <t>The receiving facility retrieves the referral from the SHR, displays it, and updates the referral status. Compare every value with the Test Data sheet and confirm with server-side evidence (IOL log, Inferno / validator report, or raw payload). Fields are grouped by screen area / FHIR resource. ★ marks critical sub-items. Screen layout is the vendor's choice.</t>
+          <t>The receiving facility retrieves the referral from the SHR, shows it, and updates the referral status. Compare every value with the Test Data sheet. Confirm with server-side evidence (IOL log, Inferno / validator report, or raw payload). Fields are grouped by screen area / FHIR resource. ★ marks critical sub-items. The vendor MAY choose the screen layout.</t>
         </is>
       </c>
     </row>
@@ -42658,7 +42829,7 @@
       </c>
       <c r="G4" s="186" t="inlineStr">
         <is>
-          <t>Count criteria: mark each sub-item (rows marked ↳). Required, Achieved, Result and Outstanding are calculated automatically.</t>
+          <t>Count criteria: mark each sub-item (rows marked ↳). The tool calculates Required, Achieved, Result and Outstanding automatically.</t>
         </is>
       </c>
     </row>
@@ -42840,7 +43011,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="125.5" customHeight="1" s="125">
+    <row r="10" ht="152.5" customHeight="1" s="125">
       <c r="A10" s="172" t="inlineStr">
         <is>
           <t>TS2-01</t>
@@ -42858,15 +43029,18 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search / subscribe for referrals addressed to the facility (e.g., by Task.owner or ServiceRequest.performer = the facility's NHFR-identified Organization). Polling, subscription or IOL notification is the vendor's choice.
-Purpose: Referrals are not missed and staff do not need IDs passed by phone.
+          <t xml:space="preserve">Search for, or subscribe to, referrals addressed to the facility. For example, use Task.owner or ServiceRequest.performer = the facility's NHFR-identified Organization. The vendor MAY choose polling, subscription or IOL notification.
+Purpose: Staff do not miss referrals and do not need to get IDs by phone.
 </t>
         </is>
       </c>
       <c r="E10" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submit the Test Data referral; Met if it appears in the receiving facility's incoming list without typing an ID.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Submit the Test Data referral. Met if it appears in the receiving facility's incoming list without typing an ID.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -42933,7 +43107,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="206.5" customHeight="1" s="125">
+    <row r="11" ht="260.5" customHeight="1" s="125">
       <c r="A11" s="172" t="inlineStr">
         <is>
           <t>TS2-02</t>
@@ -42946,12 +43120,12 @@
       </c>
       <c r="C11" s="172" t="inlineStr">
         <is>
-          <t>Referring and receiving facility details are retrieved and displayed correctly</t>
+          <t>Referring and receiving facility details are retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D11" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the Organization resources from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the Organization resources from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: The receiving clinician knows where the patient comes from and that the referral is meant for them.
 </t>
         </is>
@@ -42959,10 +43133,13 @@
       <c r="E11" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -43395,7 +43572,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="206.5" customHeight="1" s="125">
+    <row r="19" ht="260.5" customHeight="1" s="125">
       <c r="A19" s="172" t="inlineStr">
         <is>
           <t>TS2-03</t>
@@ -43408,12 +43585,12 @@
       </c>
       <c r="C19" s="172" t="inlineStr">
         <is>
-          <t>Referring practitioner (and care navigator, if assigned) is retrieved and displayed correctly</t>
+          <t>Referring practitioner (and care navigator, if assigned) is retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D19" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the referring PractitionerRole / Practitioner (ServiceRequest.requester) from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the referring PractitionerRole / Practitioner (ServiceRequest.requester) from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: The receiving facility knows whom to call back.
 </t>
         </is>
@@ -43421,10 +43598,13 @@
       <c r="E19" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -43653,7 +43833,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="206.5" customHeight="1" s="125">
+    <row r="23" ht="260.5" customHeight="1" s="125">
       <c r="A23" s="172" t="inlineStr">
         <is>
           <t>TS2-04</t>
@@ -43666,23 +43846,26 @@
       </c>
       <c r="C23" s="172" t="inlineStr">
         <is>
-          <t>Patient demographics and identifiers are retrieved and displayed correctly</t>
+          <t>Patient demographics and identifiers are retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D23" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the Patient (and RelatedPerson / Patient.contact) from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
-Purpose: The patient is identified unambiguously at the receiving facility.
+          <t xml:space="preserve">Read the Patient (and RelatedPerson / Patient.contact) from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
+Purpose: The receiving facility can identify the patient without ambiguity.
 </t>
         </is>
       </c>
       <c r="E23" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -43978,7 +44161,7 @@
       </c>
       <c r="C28" s="193" t="inlineStr">
         <is>
-          <t>Age — computed correctly from the birth date on the day of testing (display check)</t>
+          <t>Age: computed correctly from the birth date on the day of testing (display check)</t>
         </is>
       </c>
       <c r="D28" s="195" t="inlineStr">
@@ -44319,7 +44502,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="206.5" customHeight="1" s="125">
+    <row r="35" ht="260.5" customHeight="1" s="125">
       <c r="A35" s="172" t="inlineStr">
         <is>
           <t>TS2-05</t>
@@ -44332,12 +44515,12 @@
       </c>
       <c r="C35" s="172" t="inlineStr">
         <is>
-          <t>Referral request details are retrieved and displayed correctly</t>
+          <t>Referral request details are retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D35" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the ServiceRequest from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the ServiceRequest from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: The receiving facility sees what is requested, how urgent it is and why.
 </t>
         </is>
@@ -44345,10 +44528,13 @@
       <c r="E35" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -44635,7 +44821,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="206.5" customHeight="1" s="125">
+    <row r="40" ht="260.5" customHeight="1" s="125">
       <c r="A40" s="172" t="inlineStr">
         <is>
           <t>TS2-06</t>
@@ -44648,12 +44834,12 @@
       </c>
       <c r="C40" s="172" t="inlineStr">
         <is>
-          <t>Clinical findings are retrieved and displayed correctly</t>
+          <t>Clinical findings are retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D40" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the Condition and Encounter resources from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the Condition and Encounter resources from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: The receiving clinician understands the clinical picture before the patient arrives.
 </t>
         </is>
@@ -44661,10 +44847,13 @@
       <c r="E40" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -44943,7 +45132,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="206.5" customHeight="1" s="125">
+    <row r="45" ht="260.5" customHeight="1" s="125">
       <c r="A45" s="172" t="inlineStr">
         <is>
           <t>TS2-07</t>
@@ -44956,12 +45145,12 @@
       </c>
       <c r="C45" s="172" t="inlineStr">
         <is>
-          <t>Vital signs are retrieved and displayed correctly (value and unit)</t>
+          <t>Vital signs are retrieved and shown correctly (value and unit)</t>
         </is>
       </c>
       <c r="D45" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the Observation resources from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the Observation resources from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: Vital signs are shown exactly as measured.
 </t>
         </is>
@@ -44969,10 +45158,13 @@
       <c r="E45" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -45351,7 +45543,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="112" customHeight="1" s="125">
+    <row r="52" ht="139" customHeight="1" s="125">
       <c r="A52" s="172" t="inlineStr">
         <is>
           <t>TS2-08</t>
@@ -45377,7 +45569,10 @@
       <c r="E52" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">Met if the attachment sent in TS1-09 is listed with the received referral.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -45444,7 +45639,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="206.5" customHeight="1" s="125">
+    <row r="53" ht="260.5" customHeight="1" s="125">
       <c r="A53" s="172" t="inlineStr">
         <is>
           <t>TS2-09</t>
@@ -45457,12 +45652,12 @@
       </c>
       <c r="C53" s="172" t="inlineStr">
         <is>
-          <t>Treatment given and the professional signature are retrieved and displayed correctly</t>
+          <t>Treatment given and the professional signature are retrieved and shown correctly</t>
         </is>
       </c>
       <c r="D53" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the MedicationAdministration / Procedure and Provenance resources from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
+          <t xml:space="preserve">Read the MedicationAdministration / Procedure and Provenance resources from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
 Purpose: The receiving facility knows what was given and who attested the referral.
 </t>
         </is>
@@ -45470,10 +45665,13 @@
       <c r="E53" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -45698,7 +45896,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" ht="260.5" customHeight="1" s="125">
+    <row r="57" ht="314.5" customHeight="1" s="125">
       <c r="A57" s="172" t="inlineStr">
         <is>
           <t>TS2-10</t>
@@ -45716,19 +45914,23 @@
       </c>
       <c r="D57" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the receiving PractitionerRole referenced by Task.owner (and ServiceRequest.performer) from the SHR and display it in the receiving view exactly as sent — no re-typing. Screen layout and labels are the vendor's choice; the value and its meaning must match.
-Purpose: Referring and receiving practitioners share the same resource types; the system must keep them as different people (intended behaviour).
+          <t xml:space="preserve">Read the receiving PractitionerRole referenced by Task.owner (and ServiceRequest.performer) from the SHR. Show the data in the receiving view exactly as sent, with no re-typing. The vendor MAY choose the screen layout and labels. The value and its meaning MUST match.
+Purpose: Referring and receiving practitioners use the same resource types. The system MUST keep them as different people (intended behaviour).
 </t>
         </is>
       </c>
       <c r="E57" s="172" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the received Test Data referral in the receiving EMR.
-2. Compare each sub-item on screen with the Test Data value (write what is seen in Test Data column D).
-3. Confirm with the server-side evidence that the value was read from the SHR, not typed in.
-4. Assign the receiving practitioner / care navigator in the receiving EMR; confirm Task.owner on the SHR and that both practitioners appear separately on screen.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+2. Compare each sub-item on screen with the Test Data value. Write what you see in Test Data column D.
+3. Use the server-side evidence to confirm that the EMR read the value from the SHR (not from manual entry).
+4. Assign the receiving practitioner / care navigator in the receiving EMR.
+5. Confirm Task.owner on the SHR. Confirm that both practitioners appear separately on screen.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -45866,7 +46068,7 @@
       </c>
       <c r="C59" s="193" t="inlineStr">
         <is>
-          <t>Care navigator at the receiving facility — Task.owner (N/A if the facility does not assign one)</t>
+          <t>Care navigator at the receiving facility: Task.owner (N/A if the facility does not assign one)</t>
         </is>
       </c>
       <c r="D59" s="195" t="inlineStr">
@@ -45970,7 +46172,7 @@
       </c>
       <c r="C61" s="193" t="inlineStr">
         <is>
-          <t>Referring and receiving practitioners are stored and displayed as separate people — not merged or overwritten</t>
+          <t>Referring and receiving practitioners are stored and shown as separate people, not merged or overwritten</t>
         </is>
       </c>
       <c r="D61" s="195" t="inlineStr">
@@ -46011,7 +46213,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="220" customHeight="1" s="125">
+    <row r="62" ht="260.5" customHeight="1" s="125">
       <c r="A62" s="172" t="inlineStr">
         <is>
           <t>TS2-11</t>
@@ -46029,7 +46231,7 @@
       </c>
       <c r="D62" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Update the Task on the SHR when the receiving facility acts: received, then accepted or rejected (with reason in Task.statusReason), then completed (Task.executionPeriod.end). Receiving responses follow the eReferral Receiving Facility Response VS. Any update method is accepted.
+          <t xml:space="preserve">Update the Task on the SHR when the receiving facility acts. The sequence is received, then accepted or rejected (with reason in Task.statusReason), then completed (Task.executionPeriod.end). Receiving responses follow the eReferral Receiving Facility Response VS. The vendor MAY use any update method.
 Purpose: Both facilities and the dashboards see the true status of every referral.
 </t>
         </is>
@@ -46039,8 +46241,11 @@
           <t xml:space="preserve">1. In the receiving EMR, mark the Test Data referral Received, then Accepted, then Completed.
 2. Use a second test referral to Reject with a reason.
 3. Confirm each new status on the SHR with the server-side evidence. (Status timestamps are checked in TS2-13.)
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -46128,7 +46333,7 @@
       </c>
       <c r="C63" s="193" t="inlineStr">
         <is>
-          <t>Received — Task.status = received</t>
+          <t>Received: Task.status = received</t>
         </is>
       </c>
       <c r="D63" s="195" t="inlineStr">
@@ -46182,7 +46387,7 @@
       </c>
       <c r="C64" s="193" t="inlineStr">
         <is>
-          <t>Accepted — Task.status = accepted</t>
+          <t>Accepted: Task.status = accepted</t>
         </is>
       </c>
       <c r="D64" s="195" t="inlineStr">
@@ -46236,7 +46441,7 @@
       </c>
       <c r="C65" s="193" t="inlineStr">
         <is>
-          <t>Rejected with reason — Task.status = rejected + statusReason (second test referral)</t>
+          <t>Rejected with reason: Task.status = rejected + statusReason (second test referral)</t>
         </is>
       </c>
       <c r="D65" s="195" t="inlineStr">
@@ -46286,7 +46491,7 @@
       </c>
       <c r="C66" s="193" t="inlineStr">
         <is>
-          <t>Completed — Task.status = completed</t>
+          <t>Completed: Task.status = completed</t>
         </is>
       </c>
       <c r="D66" s="195" t="inlineStr">
@@ -46323,7 +46528,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="125.5" customHeight="1" s="125">
+    <row r="67" ht="152.5" customHeight="1" s="125">
       <c r="A67" s="172" t="inlineStr">
         <is>
           <t>TS2-12</t>
@@ -46341,15 +46546,18 @@
       </c>
       <c r="D67" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read the updated Task from the SHR (polling, subscription or IOL notification — vendor's choice) and show the current status to the referring facility.
+          <t xml:space="preserve">Read the updated Task from the SHR. The vendor MAY choose polling, subscription or IOL notification. Show the current status to the referring facility.
 Purpose: The referring facility knows whether the patient is expected.
 </t>
         </is>
       </c>
       <c r="E67" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change the status at the receiving EMR (TS2-11); Met if the referring EMR shows the new status, including a rejection and its reason.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">Change the status at the receiving EMR (TS2-11). Met if the referring EMR shows the new status, including a rejection and its reason.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -46416,7 +46624,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="179.5" customHeight="1" s="125">
+    <row r="68" ht="220" customHeight="1" s="125">
       <c r="A68" s="172" t="inlineStr">
         <is>
           <t>TS2-13</t>
@@ -46429,21 +46637,24 @@
       </c>
       <c r="C68" s="172" t="inlineStr">
         <is>
-          <t>Every status change of the referral is time-stamped and kept: requested, received, accepted / rejected, completed (moved from L4-06; Connectathon Issue #26)</t>
+          <t>Every status change of the referral is time-stamped and kept: requested, received, accepted / rejected, completed (moved from L4-06, Connectathon Issue #26)</t>
         </is>
       </c>
       <c r="D68" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record the date/time of each Task status change so the history can be read back (Task history / versions, Provenance, or Task.lastModified per update — vendor's choice; ERefTask marks authoredOn and lastModified as Must Support). Earlier timestamps must not be overwritten.
-Purpose: Needed for audit and for turnaround time (IND-08).
+          <t xml:space="preserve">Record the date/time of each Task status change so that it is possible to read the history later. The vendor MAY use Task history / versions, Provenance, or Task.lastModified per update. ERefTask marks authoredOn and lastModified as Must Support. Earlier timestamps MUST NOT be overwritten.
+Purpose: The history is necessary for audit and for turnaround time (IND-08).
 </t>
         </is>
       </c>
       <c r="E68" s="172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Validator (server-side) reads the Task history (_history) or the linked Provenance on the SHR after TS2-11. Count the 4 status changes that have a date/time that matches when they were made.
-Mark each sub-item (↳) below; Achieved is counted automatically. ★ = critical sub-item: if it is Not Met (or N/A) the criterion counts as a critical failure.
-Server-side evidence — any ONE of: (a) Interoperability Layer transaction log (e.g., OpenHIM), (b) Inferno / official FHIR validator report, or (c) the raw FHIR request / response payload provided by the developer and captured during the session.
+          <t xml:space="preserve">After TS2-11, the validator (server-side) reads the Task history (_history) or the linked Provenance on the SHR. Count the 4 status changes that have a date/time that matches when they were made.
+Mark each sub-item (↳) below. The tool counts Achieved automatically. ★ = critical sub-item. If a ★ sub-item is Not Met (or N/A), the criterion counts as a critical failure.
+Server-side evidence is any one of these items:
+(a) The Interoperability Layer transaction log (for example, OpenHIM).
+(b) An Inferno / official FHIR validator report.
+(c) The raw FHIR request / response payload that the developer provides and that is captured during the session.
 </t>
         </is>
       </c>
@@ -46531,7 +46742,7 @@
       </c>
       <c r="C69" s="193" t="inlineStr">
         <is>
-          <t>Requested — date/time recorded (Task.authoredOn)</t>
+          <t>Requested: date/time recorded (Task.authoredOn)</t>
         </is>
       </c>
       <c r="D69" s="195" t="inlineStr">
@@ -46585,7 +46796,7 @@
       </c>
       <c r="C70" s="193" t="inlineStr">
         <is>
-          <t>Received — date/time recorded and kept (absorbs Rev 6 TS2-11.5)</t>
+          <t>Received: date/time recorded and kept (absorbs Rev 6 TS2-11.5)</t>
         </is>
       </c>
       <c r="D70" s="195" t="inlineStr">
@@ -46639,7 +46850,7 @@
       </c>
       <c r="C71" s="193" t="inlineStr">
         <is>
-          <t>Accepted / rejected — date/time recorded and kept</t>
+          <t>Accepted / rejected: date/time recorded and kept</t>
         </is>
       </c>
       <c r="D71" s="195" t="inlineStr">
@@ -46693,7 +46904,7 @@
       </c>
       <c r="C72" s="193" t="inlineStr">
         <is>
-          <t>Completed — date/time recorded and kept</t>
+          <t>Completed: date/time recorded and kept</t>
         </is>
       </c>
       <c r="D72" s="195" t="inlineStr">
@@ -46793,7 +47004,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 54cc0be · built 2026-10-19 17:40 PHT</oddHeader>
+    <oddHeader>&amp;R&amp;7 Version unreleased draft · branch main · commit 35e735e · built 2026-10-26 11:18 PHT</oddHeader>
     <oddFooter>&amp;C&amp;7 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
